--- a/router/output/claude_sonnet/2026-02-25_line_by_line_report_merged - コピー.xlsx
+++ b/router/output/claude_sonnet/2026-02-25_line_by_line_report_merged - コピー.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Develop\Skills\MySkills\router\output\claude_sonnet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Develop\Gakusyu\router\output\claude_sonnet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980B826A-19F1-4966-8918-75B4947E0AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EC359D-9A3D-400D-AB4F-73D37101416B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="28920" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5919,7 +5919,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5939,18 +5939,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -5981,7 +5969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5994,12 +5982,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6323,7 +6305,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6333,24 +6315,24 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -6376,7 +6358,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -6402,7 +6384,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6428,7 +6410,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -6454,7 +6436,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -6480,7 +6462,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -6506,7 +6488,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -6532,7 +6514,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -6558,7 +6540,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -6584,7 +6566,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -6609,8 +6591,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -6636,7 +6618,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -6662,7 +6644,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -6688,7 +6670,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -6714,7 +6696,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -6740,7 +6722,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -6766,7 +6748,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -6791,8 +6773,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A19" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -6817,8 +6799,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A20" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -6843,8 +6825,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A21" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -6869,8 +6851,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A22" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -6896,7 +6878,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -6922,7 +6904,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -6948,7 +6930,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -6974,7 +6956,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -7000,7 +6982,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -7026,7 +7008,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -7052,7 +7034,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -7078,7 +7060,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -7104,7 +7086,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -7130,7 +7112,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7156,7 +7138,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -7182,7 +7164,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -7208,7 +7190,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -7234,7 +7216,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -7260,7 +7242,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -7286,7 +7268,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -7312,7 +7294,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -7338,7 +7320,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -7364,7 +7346,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -7390,7 +7372,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -7416,7 +7398,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -7442,7 +7424,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -7468,7 +7450,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -7494,7 +7476,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -7519,8 +7501,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A47" s="8" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A47" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -7546,7 +7528,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -7572,7 +7554,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -7598,7 +7580,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -7624,7 +7606,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -7650,7 +7632,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -7676,7 +7658,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -7702,7 +7684,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -7728,7 +7710,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -7754,7 +7736,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -7780,7 +7762,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -7806,7 +7788,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -7832,7 +7814,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -7858,7 +7840,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -7883,8 +7865,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A61" s="8" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A61" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -7910,7 +7892,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -7936,7 +7918,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -7962,7 +7944,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -7987,8 +7969,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A65" s="8" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A65" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -8014,7 +7996,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -8039,8 +8021,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A67" s="8" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A67" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -8066,7 +8048,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -8092,7 +8074,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -8118,7 +8100,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -8144,7 +8126,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -8170,7 +8152,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -8196,7 +8178,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -8222,7 +8204,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -8248,7 +8230,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -8274,7 +8256,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -8300,7 +8282,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -8326,7 +8308,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -8352,7 +8334,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -8378,7 +8360,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -8404,7 +8386,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -8430,7 +8412,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -8456,7 +8438,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -8482,7 +8464,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A84" s="8" t="s">
+      <c r="A84" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -8507,8 +8489,8 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A85" s="8" t="s">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A85" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -8534,7 +8516,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -8560,7 +8542,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -8586,7 +8568,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -8612,7 +8594,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -8638,7 +8620,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -8664,7 +8646,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -8690,7 +8672,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -8716,7 +8698,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B93" s="3" t="s">
@@ -8742,7 +8724,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -8768,7 +8750,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -8794,7 +8776,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -8820,7 +8802,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -8846,7 +8828,7 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -8872,7 +8854,7 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B99" s="3" t="s">
@@ -8898,7 +8880,7 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -8924,7 +8906,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -8950,7 +8932,7 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -8976,7 +8958,7 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B103" s="3" t="s">
@@ -9002,7 +8984,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A104" s="8" t="s">
+      <c r="A104" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -9028,7 +9010,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B105" s="3" t="s">
@@ -9054,7 +9036,7 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -9080,7 +9062,7 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B107" s="3" t="s">
@@ -9106,7 +9088,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -9132,7 +9114,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B109" s="3" t="s">
@@ -9158,7 +9140,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A110" s="8" t="s">
+      <c r="A110" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -9184,7 +9166,7 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B111" s="3" t="s">
@@ -9210,7 +9192,7 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A112" s="8" t="s">
+      <c r="A112" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -9236,7 +9218,7 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B113" s="3" t="s">
@@ -9262,7 +9244,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A114" s="8" t="s">
+      <c r="A114" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -9288,7 +9270,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A115" s="8" t="s">
+      <c r="A115" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B115" s="3" t="s">
@@ -9314,7 +9296,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A116" s="8" t="s">
+      <c r="A116" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -9340,7 +9322,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B117" s="3" t="s">
@@ -9365,8 +9347,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A118" s="8" t="s">
+    <row r="118" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A118" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -9391,8 +9373,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A119" s="8" t="s">
+    <row r="119" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A119" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B119" s="3" t="s">
@@ -9418,7 +9400,7 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -9444,7 +9426,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B121" s="3" t="s">
@@ -9470,7 +9452,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A122" s="8" t="s">
+      <c r="A122" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B122" s="2" t="s">
@@ -9496,7 +9478,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B123" s="3" t="s">
@@ -9522,7 +9504,7 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A124" s="8" t="s">
+      <c r="A124" s="6" t="s">
         <v>318</v>
       </c>
       <c r="B124" s="2" t="s">
@@ -9548,7 +9530,7 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A125" s="8" t="s">
+      <c r="A125" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B125" s="3" t="s">
@@ -9573,8 +9555,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A126" s="8" t="s">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A126" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -9600,7 +9582,7 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B127" s="3" t="s">
@@ -9626,7 +9608,7 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A128" s="8" t="s">
+      <c r="A128" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B128" s="2" t="s">
@@ -9651,8 +9633,8 @@
         <v>329</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A129" s="8" t="s">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A129" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B129" s="3" t="s">
@@ -9678,7 +9660,7 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A130" s="8" t="s">
+      <c r="A130" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B130" s="2" t="s">
@@ -9704,7 +9686,7 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B131" s="3" t="s">
@@ -9730,7 +9712,7 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A132" s="8" t="s">
+      <c r="A132" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B132" s="2" t="s">
@@ -9756,7 +9738,7 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B133" s="3" t="s">
@@ -9782,7 +9764,7 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A134" s="8" t="s">
+      <c r="A134" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B134" s="2" t="s">
@@ -9807,8 +9789,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="45" x14ac:dyDescent="0.15">
-      <c r="A135" s="8" t="s">
+    <row r="135" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
+      <c r="A135" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B135" s="3" t="s">
@@ -9834,7 +9816,7 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A136" s="8" t="s">
+      <c r="A136" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B136" s="2" t="s">
@@ -9859,8 +9841,8 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A137" s="8" t="s">
+    <row r="137" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A137" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B137" s="3" t="s">
@@ -9885,8 +9867,8 @@
         <v>437</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A138" s="8" t="s">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A138" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B138" s="2" t="s">
@@ -9911,8 +9893,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A139" s="8" t="s">
+    <row r="139" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A139" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B139" s="3" t="s">
@@ -9937,8 +9919,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A140" s="8" t="s">
+    <row r="140" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A140" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B140" s="2" t="s">
@@ -9964,7 +9946,7 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B141" s="3" t="s">
@@ -9990,7 +9972,7 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A142" s="8" t="s">
+      <c r="A142" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B142" s="2" t="s">
@@ -10016,7 +9998,7 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B143" s="3" t="s">
@@ -10042,7 +10024,7 @@
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A144" s="8" t="s">
+      <c r="A144" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B144" s="2" t="s">
@@ -10068,7 +10050,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B145" s="3" t="s">
@@ -10094,7 +10076,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A146" s="8" t="s">
+      <c r="A146" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B146" s="2" t="s">
@@ -10119,8 +10101,8 @@
         <v>396</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A147" s="8" t="s">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A147" s="6" t="s">
         <v>402</v>
       </c>
       <c r="B147" s="3" t="s">
@@ -10146,7 +10128,7 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A148" s="8" t="s">
+      <c r="A148" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B148" s="2" t="s">
@@ -10171,8 +10153,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A149" s="8" t="s">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A149" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B149" s="3" t="s">
@@ -10198,7 +10180,7 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A150" s="8" t="s">
+      <c r="A150" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -10224,7 +10206,7 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A151" s="8" t="s">
+      <c r="A151" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B151" s="3" t="s">
@@ -10249,8 +10231,8 @@
         <v>329</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A152" s="8" t="s">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A152" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -10276,7 +10258,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A153" s="8" t="s">
+      <c r="A153" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B153" s="3" t="s">
@@ -10302,7 +10284,7 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A154" s="8" t="s">
+      <c r="A154" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -10328,7 +10310,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B155" s="3" t="s">
@@ -10354,7 +10336,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A156" s="8" t="s">
+      <c r="A156" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -10380,7 +10362,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A157" s="8" t="s">
+      <c r="A157" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B157" s="3" t="s">
@@ -10406,7 +10388,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A158" s="8" t="s">
+      <c r="A158" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -10432,7 +10414,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A159" s="8" t="s">
+      <c r="A159" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B159" s="3" t="s">
@@ -10457,8 +10439,8 @@
         <v>367</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A160" s="8" t="s">
+    <row r="160" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A160" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -10483,8 +10465,8 @@
         <v>437</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A161" s="8" t="s">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A161" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B161" s="3" t="s">
@@ -10509,8 +10491,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A162" s="8" t="s">
+    <row r="162" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A162" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -10535,8 +10517,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A163" s="8" t="s">
+    <row r="163" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A163" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B163" s="3" t="s">
@@ -10562,7 +10544,7 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A164" s="8" t="s">
+      <c r="A164" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -10588,7 +10570,7 @@
       </c>
     </row>
     <row r="165" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A165" s="8" t="s">
+      <c r="A165" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B165" s="3" t="s">
@@ -10614,7 +10596,7 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A166" s="8" t="s">
+      <c r="A166" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B166" s="2" t="s">
@@ -10640,7 +10622,7 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A167" s="8" t="s">
+      <c r="A167" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B167" s="3" t="s">
@@ -10666,7 +10648,7 @@
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A168" s="8" t="s">
+      <c r="A168" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -10692,7 +10674,7 @@
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A169" s="8" t="s">
+      <c r="A169" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B169" s="3" t="s">
@@ -10717,8 +10699,8 @@
         <v>396</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A170" s="8" t="s">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A170" s="6" t="s">
         <v>460</v>
       </c>
       <c r="B170" s="2" t="s">
@@ -10744,7 +10726,7 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A171" s="8" t="s">
+      <c r="A171" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B171" s="3" t="s">
@@ -10769,8 +10751,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A172" s="8" t="s">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A172" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B172" s="2" t="s">
@@ -10796,7 +10778,7 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A173" s="8" t="s">
+      <c r="A173" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B173" s="3" t="s">
@@ -10822,7 +10804,7 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A174" s="8" t="s">
+      <c r="A174" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B174" s="2" t="s">
@@ -10847,8 +10829,8 @@
         <v>329</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A175" s="8" t="s">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A175" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B175" s="3" t="s">
@@ -10874,7 +10856,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A176" s="8" t="s">
+      <c r="A176" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -10900,7 +10882,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A177" s="8" t="s">
+      <c r="A177" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B177" s="3" t="s">
@@ -10926,7 +10908,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A178" s="8" t="s">
+      <c r="A178" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B178" s="2" t="s">
@@ -10952,7 +10934,7 @@
       </c>
     </row>
     <row r="179" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A179" s="8" t="s">
+      <c r="A179" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B179" s="3" t="s">
@@ -10978,7 +10960,7 @@
       </c>
     </row>
     <row r="180" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A180" s="8" t="s">
+      <c r="A180" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B180" s="2" t="s">
@@ -11004,7 +10986,7 @@
       </c>
     </row>
     <row r="181" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A181" s="8" t="s">
+      <c r="A181" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B181" s="3" t="s">
@@ -11030,7 +11012,7 @@
       </c>
     </row>
     <row r="182" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A182" s="8" t="s">
+      <c r="A182" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -11055,8 +11037,8 @@
         <v>367</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A183" s="8" t="s">
+    <row r="183" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A183" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B183" s="3" t="s">
@@ -11081,8 +11063,8 @@
         <v>437</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A184" s="8" t="s">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A184" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -11107,8 +11089,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A185" s="8" t="s">
+    <row r="185" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A185" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B185" s="3" t="s">
@@ -11133,8 +11115,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A186" s="8" t="s">
+    <row r="186" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A186" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -11160,7 +11142,7 @@
       </c>
     </row>
     <row r="187" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A187" s="8" t="s">
+      <c r="A187" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B187" s="3" t="s">
@@ -11186,7 +11168,7 @@
       </c>
     </row>
     <row r="188" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A188" s="8" t="s">
+      <c r="A188" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B188" s="2" t="s">
@@ -11212,7 +11194,7 @@
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A189" s="8" t="s">
+      <c r="A189" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B189" s="3" t="s">
@@ -11238,7 +11220,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A190" s="8" t="s">
+      <c r="A190" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B190" s="2" t="s">
@@ -11264,7 +11246,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B191" s="3" t="s">
@@ -11290,7 +11272,7 @@
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A192" s="8" t="s">
+      <c r="A192" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B192" s="2" t="s">
@@ -11315,8 +11297,8 @@
         <v>396</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A193" s="8" t="s">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A193" s="6" t="s">
         <v>503</v>
       </c>
       <c r="B193" s="3" t="s">
@@ -11342,7 +11324,7 @@
       </c>
     </row>
     <row r="194" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A194" s="8" t="s">
+      <c r="A194" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -11368,7 +11350,7 @@
       </c>
     </row>
     <row r="195" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A195" s="8" t="s">
+      <c r="A195" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B195" s="3" t="s">
@@ -11394,7 +11376,7 @@
       </c>
     </row>
     <row r="196" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A196" s="8" t="s">
+      <c r="A196" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B196" s="2" t="s">
@@ -11420,7 +11402,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A197" s="8" t="s">
+      <c r="A197" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B197" s="3" t="s">
@@ -11446,7 +11428,7 @@
       </c>
     </row>
     <row r="198" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A198" s="8" t="s">
+      <c r="A198" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B198" s="2" t="s">
@@ -11472,7 +11454,7 @@
       </c>
     </row>
     <row r="199" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A199" s="8" t="s">
+      <c r="A199" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B199" s="3" t="s">
@@ -11498,7 +11480,7 @@
       </c>
     </row>
     <row r="200" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A200" s="8" t="s">
+      <c r="A200" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -11524,7 +11506,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A201" s="8" t="s">
+      <c r="A201" s="6" t="s">
         <v>546</v>
       </c>
       <c r="B201" s="3" t="s">
@@ -11550,7 +11532,7 @@
       </c>
     </row>
     <row r="202" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A202" s="8" t="s">
+      <c r="A202" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -11576,7 +11558,7 @@
       </c>
     </row>
     <row r="203" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A203" s="8" t="s">
+      <c r="A203" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B203" s="3" t="s">
@@ -11602,7 +11584,7 @@
       </c>
     </row>
     <row r="204" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A204" s="8" t="s">
+      <c r="A204" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B204" s="2" t="s">
@@ -11628,7 +11610,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A205" s="8" t="s">
+      <c r="A205" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B205" s="3" t="s">
@@ -11654,7 +11636,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A206" s="8" t="s">
+      <c r="A206" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B206" s="2" t="s">
@@ -11680,7 +11662,7 @@
       </c>
     </row>
     <row r="207" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A207" s="8" t="s">
+      <c r="A207" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B207" s="3" t="s">
@@ -11706,7 +11688,7 @@
       </c>
     </row>
     <row r="208" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A208" s="8" t="s">
+      <c r="A208" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B208" s="2" t="s">
@@ -11731,8 +11713,8 @@
         <v>252</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A209" s="8" t="s">
+    <row r="209" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A209" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B209" s="3" t="s">
@@ -11758,7 +11740,7 @@
       </c>
     </row>
     <row r="210" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A210" s="8" t="s">
+      <c r="A210" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B210" s="2" t="s">
@@ -11784,7 +11766,7 @@
       </c>
     </row>
     <row r="211" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A211" s="8" t="s">
+      <c r="A211" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B211" s="3" t="s">
@@ -11810,7 +11792,7 @@
       </c>
     </row>
     <row r="212" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A212" s="8" t="s">
+      <c r="A212" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B212" s="2" t="s">
@@ -11836,7 +11818,7 @@
       </c>
     </row>
     <row r="213" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A213" s="8" t="s">
+      <c r="A213" s="6" t="s">
         <v>566</v>
       </c>
       <c r="B213" s="3" t="s">
@@ -11862,7 +11844,7 @@
       </c>
     </row>
     <row r="214" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A214" s="8" t="s">
+      <c r="A214" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B214" s="2" t="s">
@@ -11888,7 +11870,7 @@
       </c>
     </row>
     <row r="215" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A215" s="8" t="s">
+      <c r="A215" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B215" s="3" t="s">
@@ -11914,7 +11896,7 @@
       </c>
     </row>
     <row r="216" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A216" s="8" t="s">
+      <c r="A216" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B216" s="2" t="s">
@@ -11940,7 +11922,7 @@
       </c>
     </row>
     <row r="217" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A217" s="8" t="s">
+      <c r="A217" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B217" s="3" t="s">
@@ -11966,7 +11948,7 @@
       </c>
     </row>
     <row r="218" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A218" s="8" t="s">
+      <c r="A218" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B218" s="2" t="s">
@@ -11992,7 +11974,7 @@
       </c>
     </row>
     <row r="219" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A219" s="8" t="s">
+      <c r="A219" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B219" s="3" t="s">
@@ -12018,7 +12000,7 @@
       </c>
     </row>
     <row r="220" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A220" s="8" t="s">
+      <c r="A220" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B220" s="2" t="s">
@@ -12044,7 +12026,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A221" s="8" t="s">
+      <c r="A221" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B221" s="3" t="s">
@@ -12070,7 +12052,7 @@
       </c>
     </row>
     <row r="222" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A222" s="8" t="s">
+      <c r="A222" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B222" s="2" t="s">
@@ -12096,7 +12078,7 @@
       </c>
     </row>
     <row r="223" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A223" s="8" t="s">
+      <c r="A223" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B223" s="3" t="s">
@@ -12122,7 +12104,7 @@
       </c>
     </row>
     <row r="224" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A224" s="8" t="s">
+      <c r="A224" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -12148,7 +12130,7 @@
       </c>
     </row>
     <row r="225" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A225" s="8" t="s">
+      <c r="A225" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B225" s="3" t="s">
@@ -12174,7 +12156,7 @@
       </c>
     </row>
     <row r="226" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A226" s="8" t="s">
+      <c r="A226" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -12200,7 +12182,7 @@
       </c>
     </row>
     <row r="227" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A227" s="8" t="s">
+      <c r="A227" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B227" s="3" t="s">
@@ -12225,8 +12207,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A228" s="8" t="s">
+    <row r="228" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A228" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B228" s="2" t="s">
@@ -12251,8 +12233,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A229" s="8" t="s">
+    <row r="229" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A229" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B229" s="3" t="s">
@@ -12278,7 +12260,7 @@
       </c>
     </row>
     <row r="230" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A230" s="8" t="s">
+      <c r="A230" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B230" s="2" t="s">
@@ -12304,7 +12286,7 @@
       </c>
     </row>
     <row r="231" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A231" s="8" t="s">
+      <c r="A231" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B231" s="3" t="s">
@@ -12330,7 +12312,7 @@
       </c>
     </row>
     <row r="232" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A232" s="8" t="s">
+      <c r="A232" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B232" s="2" t="s">
@@ -12356,7 +12338,7 @@
       </c>
     </row>
     <row r="233" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A233" s="8" t="s">
+      <c r="A233" s="6" t="s">
         <v>601</v>
       </c>
       <c r="B233" s="3" t="s">
@@ -12382,7 +12364,7 @@
       </c>
     </row>
     <row r="234" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A234" s="8" t="s">
+      <c r="A234" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B234" s="2" t="s">
@@ -12408,7 +12390,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A235" s="8" t="s">
+      <c r="A235" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B235" s="3" t="s">
@@ -12434,7 +12416,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A236" s="8" t="s">
+      <c r="A236" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B236" s="2" t="s">
@@ -12460,7 +12442,7 @@
       </c>
     </row>
     <row r="237" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A237" s="8" t="s">
+      <c r="A237" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B237" s="3" t="s">
@@ -12486,7 +12468,7 @@
       </c>
     </row>
     <row r="238" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A238" s="8" t="s">
+      <c r="A238" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B238" s="2" t="s">
@@ -12512,7 +12494,7 @@
       </c>
     </row>
     <row r="239" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A239" s="8" t="s">
+      <c r="A239" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B239" s="3" t="s">
@@ -12538,7 +12520,7 @@
       </c>
     </row>
     <row r="240" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A240" s="8" t="s">
+      <c r="A240" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B240" s="2" t="s">
@@ -12564,7 +12546,7 @@
       </c>
     </row>
     <row r="241" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A241" s="8" t="s">
+      <c r="A241" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B241" s="3" t="s">
@@ -12590,7 +12572,7 @@
       </c>
     </row>
     <row r="242" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A242" s="8" t="s">
+      <c r="A242" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B242" s="2" t="s">
@@ -12616,7 +12598,7 @@
       </c>
     </row>
     <row r="243" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A243" s="8" t="s">
+      <c r="A243" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B243" s="3" t="s">
@@ -12642,7 +12624,7 @@
       </c>
     </row>
     <row r="244" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A244" s="8" t="s">
+      <c r="A244" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B244" s="2" t="s">
@@ -12668,7 +12650,7 @@
       </c>
     </row>
     <row r="245" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A245" s="8" t="s">
+      <c r="A245" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B245" s="3" t="s">
@@ -12694,7 +12676,7 @@
       </c>
     </row>
     <row r="246" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A246" s="8" t="s">
+      <c r="A246" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B246" s="2" t="s">
@@ -12720,7 +12702,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A247" s="8" t="s">
+      <c r="A247" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B247" s="3" t="s">
@@ -12746,7 +12728,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A248" s="8" t="s">
+      <c r="A248" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B248" s="2" t="s">
@@ -12772,7 +12754,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A249" s="8" t="s">
+      <c r="A249" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B249" s="3" t="s">
@@ -12798,7 +12780,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A250" s="8" t="s">
+      <c r="A250" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B250" s="2" t="s">
@@ -12824,7 +12806,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A251" s="8" t="s">
+      <c r="A251" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B251" s="3" t="s">
@@ -12850,7 +12832,7 @@
       </c>
     </row>
     <row r="252" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A252" s="8" t="s">
+      <c r="A252" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B252" s="2" t="s">
@@ -12876,7 +12858,7 @@
       </c>
     </row>
     <row r="253" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A253" s="8" t="s">
+      <c r="A253" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B253" s="3" t="s">
@@ -12902,7 +12884,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A254" s="8" t="s">
+      <c r="A254" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B254" s="2" t="s">
@@ -12928,7 +12910,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A255" s="8" t="s">
+      <c r="A255" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B255" s="3" t="s">
@@ -12954,7 +12936,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A256" s="8" t="s">
+      <c r="A256" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B256" s="2" t="s">
@@ -12980,7 +12962,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A257" s="8" t="s">
+      <c r="A257" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B257" s="3" t="s">
@@ -13006,7 +12988,7 @@
       </c>
     </row>
     <row r="258" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A258" s="8" t="s">
+      <c r="A258" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B258" s="2" t="s">
@@ -13032,7 +13014,7 @@
       </c>
     </row>
     <row r="259" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A259" s="8" t="s">
+      <c r="A259" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B259" s="3" t="s">
@@ -13058,7 +13040,7 @@
       </c>
     </row>
     <row r="260" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A260" s="8" t="s">
+      <c r="A260" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B260" s="2" t="s">
@@ -13084,7 +13066,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A261" s="8" t="s">
+      <c r="A261" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B261" s="3" t="s">
@@ -13110,7 +13092,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A262" s="8" t="s">
+      <c r="A262" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B262" s="2" t="s">
@@ -13136,7 +13118,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A263" s="8" t="s">
+      <c r="A263" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B263" s="3" t="s">
@@ -13162,7 +13144,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A264" s="8" t="s">
+      <c r="A264" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B264" s="2" t="s">
@@ -13188,7 +13170,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A265" s="8" t="s">
+      <c r="A265" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B265" s="3" t="s">
@@ -13214,7 +13196,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A266" s="8" t="s">
+      <c r="A266" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B266" s="2" t="s">
@@ -13240,7 +13222,7 @@
       </c>
     </row>
     <row r="267" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A267" s="8" t="s">
+      <c r="A267" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B267" s="3" t="s">
@@ -13266,7 +13248,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A268" s="8" t="s">
+      <c r="A268" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B268" s="2" t="s">
@@ -13292,7 +13274,7 @@
       </c>
     </row>
     <row r="269" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A269" s="8" t="s">
+      <c r="A269" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B269" s="3" t="s">
@@ -13318,7 +13300,7 @@
       </c>
     </row>
     <row r="270" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A270" s="8" t="s">
+      <c r="A270" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B270" s="2" t="s">
@@ -13344,7 +13326,7 @@
       </c>
     </row>
     <row r="271" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A271" s="8" t="s">
+      <c r="A271" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B271" s="3" t="s">
@@ -13370,7 +13352,7 @@
       </c>
     </row>
     <row r="272" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A272" s="8" t="s">
+      <c r="A272" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B272" s="2" t="s">
@@ -13396,7 +13378,7 @@
       </c>
     </row>
     <row r="273" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A273" s="8" t="s">
+      <c r="A273" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B273" s="3" t="s">
@@ -13422,7 +13404,7 @@
       </c>
     </row>
     <row r="274" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A274" s="8" t="s">
+      <c r="A274" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B274" s="2" t="s">
@@ -13448,7 +13430,7 @@
       </c>
     </row>
     <row r="275" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A275" s="8" t="s">
+      <c r="A275" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B275" s="3" t="s">
@@ -13474,7 +13456,7 @@
       </c>
     </row>
     <row r="276" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A276" s="8" t="s">
+      <c r="A276" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B276" s="2" t="s">
@@ -13500,7 +13482,7 @@
       </c>
     </row>
     <row r="277" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A277" s="8" t="s">
+      <c r="A277" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B277" s="3" t="s">
@@ -13526,7 +13508,7 @@
       </c>
     </row>
     <row r="278" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A278" s="8" t="s">
+      <c r="A278" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B278" s="2" t="s">
@@ -13552,7 +13534,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A279" s="8" t="s">
+      <c r="A279" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B279" s="3" t="s">
@@ -13578,7 +13560,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A280" s="8" t="s">
+      <c r="A280" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B280" s="2" t="s">
@@ -13604,7 +13586,7 @@
       </c>
     </row>
     <row r="281" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A281" s="8" t="s">
+      <c r="A281" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B281" s="3" t="s">
@@ -13630,7 +13612,7 @@
       </c>
     </row>
     <row r="282" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A282" s="8" t="s">
+      <c r="A282" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B282" s="2" t="s">
@@ -13656,7 +13638,7 @@
       </c>
     </row>
     <row r="283" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A283" s="8" t="s">
+      <c r="A283" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B283" s="3" t="s">
@@ -13682,7 +13664,7 @@
       </c>
     </row>
     <row r="284" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A284" s="8" t="s">
+      <c r="A284" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B284" s="2" t="s">
@@ -13708,7 +13690,7 @@
       </c>
     </row>
     <row r="285" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A285" s="8" t="s">
+      <c r="A285" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B285" s="3" t="s">
@@ -13734,7 +13716,7 @@
       </c>
     </row>
     <row r="286" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A286" s="8" t="s">
+      <c r="A286" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B286" s="2" t="s">
@@ -13760,7 +13742,7 @@
       </c>
     </row>
     <row r="287" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A287" s="8" t="s">
+      <c r="A287" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B287" s="3" t="s">
@@ -13786,7 +13768,7 @@
       </c>
     </row>
     <row r="288" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A288" s="8" t="s">
+      <c r="A288" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B288" s="2" t="s">
@@ -13812,7 +13794,7 @@
       </c>
     </row>
     <row r="289" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A289" s="8" t="s">
+      <c r="A289" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B289" s="3" t="s">
@@ -13838,7 +13820,7 @@
       </c>
     </row>
     <row r="290" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A290" s="8" t="s">
+      <c r="A290" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B290" s="2" t="s">
@@ -13864,7 +13846,7 @@
       </c>
     </row>
     <row r="291" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A291" s="8" t="s">
+      <c r="A291" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B291" s="3" t="s">
@@ -13890,7 +13872,7 @@
       </c>
     </row>
     <row r="292" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A292" s="8" t="s">
+      <c r="A292" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B292" s="2" t="s">
@@ -13916,7 +13898,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A293" s="8" t="s">
+      <c r="A293" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B293" s="3" t="s">
@@ -13942,7 +13924,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A294" s="8" t="s">
+      <c r="A294" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B294" s="2" t="s">
@@ -13968,7 +13950,7 @@
       </c>
     </row>
     <row r="295" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A295" s="8" t="s">
+      <c r="A295" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B295" s="3" t="s">
@@ -13994,7 +13976,7 @@
       </c>
     </row>
     <row r="296" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A296" s="8" t="s">
+      <c r="A296" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B296" s="2" t="s">
@@ -14020,7 +14002,7 @@
       </c>
     </row>
     <row r="297" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A297" s="8" t="s">
+      <c r="A297" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B297" s="3" t="s">
@@ -14046,7 +14028,7 @@
       </c>
     </row>
     <row r="298" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A298" s="8" t="s">
+      <c r="A298" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B298" s="2" t="s">
@@ -14072,7 +14054,7 @@
       </c>
     </row>
     <row r="299" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A299" s="8" t="s">
+      <c r="A299" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B299" s="3" t="s">
@@ -14098,7 +14080,7 @@
       </c>
     </row>
     <row r="300" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A300" s="8" t="s">
+      <c r="A300" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B300" s="2" t="s">
@@ -14124,7 +14106,7 @@
       </c>
     </row>
     <row r="301" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A301" s="8" t="s">
+      <c r="A301" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B301" s="3" t="s">
@@ -14150,7 +14132,7 @@
       </c>
     </row>
     <row r="302" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A302" s="8" t="s">
+      <c r="A302" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B302" s="2" t="s">
@@ -14176,7 +14158,7 @@
       </c>
     </row>
     <row r="303" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A303" s="8" t="s">
+      <c r="A303" s="6" t="s">
         <v>637</v>
       </c>
       <c r="B303" s="3" t="s">
@@ -14202,7 +14184,7 @@
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A304" s="8" t="s">
+      <c r="A304" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B304" s="2" t="s">
@@ -14228,7 +14210,7 @@
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A305" s="8" t="s">
+      <c r="A305" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B305" s="3" t="s">
@@ -14254,7 +14236,7 @@
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A306" s="8" t="s">
+      <c r="A306" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B306" s="2" t="s">
@@ -14280,7 +14262,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A307" s="8" t="s">
+      <c r="A307" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B307" s="3" t="s">
@@ -14306,7 +14288,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A308" s="8" t="s">
+      <c r="A308" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B308" s="2" t="s">
@@ -14332,7 +14314,7 @@
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A309" s="8" t="s">
+      <c r="A309" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B309" s="3" t="s">
@@ -14358,7 +14340,7 @@
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A310" s="8" t="s">
+      <c r="A310" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B310" s="2" t="s">
@@ -14384,7 +14366,7 @@
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A311" s="8" t="s">
+      <c r="A311" s="6" t="s">
         <v>767</v>
       </c>
       <c r="B311" s="3" t="s">
@@ -14409,8 +14391,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A312" s="8" t="s">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A312" s="6" t="s">
         <v>785</v>
       </c>
       <c r="B312" s="2" t="s">
@@ -14435,8 +14417,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="313" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A313" s="8" t="s">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A313" s="6" t="s">
         <v>785</v>
       </c>
       <c r="B313" s="3" t="s">
@@ -14461,8 +14443,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="314" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A314" s="8" t="s">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A314" s="6" t="s">
         <v>785</v>
       </c>
       <c r="B314" s="2" t="s">
@@ -14487,8 +14469,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A315" s="8" t="s">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A315" s="6" t="s">
         <v>785</v>
       </c>
       <c r="B315" s="3" t="s">
@@ -14513,8 +14495,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A316" s="8" t="s">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A316" s="6" t="s">
         <v>785</v>
       </c>
       <c r="B316" s="2" t="s">
@@ -14540,7 +14522,7 @@
       </c>
     </row>
     <row r="317" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A317" s="8" t="s">
+      <c r="A317" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B317" s="3" t="s">
@@ -14566,7 +14548,7 @@
       </c>
     </row>
     <row r="318" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A318" s="8" t="s">
+      <c r="A318" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B318" s="2" t="s">
@@ -14592,7 +14574,7 @@
       </c>
     </row>
     <row r="319" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A319" s="8" t="s">
+      <c r="A319" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B319" s="3" t="s">
@@ -14618,7 +14600,7 @@
       </c>
     </row>
     <row r="320" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A320" s="8" t="s">
+      <c r="A320" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B320" s="2" t="s">
@@ -14644,7 +14626,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A321" s="8" t="s">
+      <c r="A321" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B321" s="3" t="s">
@@ -14670,7 +14652,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A322" s="8" t="s">
+      <c r="A322" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B322" s="2" t="s">
@@ -14696,7 +14678,7 @@
       </c>
     </row>
     <row r="323" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A323" s="8" t="s">
+      <c r="A323" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B323" s="3" t="s">
@@ -14722,7 +14704,7 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A324" s="8" t="s">
+      <c r="A324" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B324" s="2" t="s">
@@ -14748,7 +14730,7 @@
       </c>
     </row>
     <row r="325" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A325" s="8" t="s">
+      <c r="A325" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B325" s="3" t="s">
@@ -14774,7 +14756,7 @@
       </c>
     </row>
     <row r="326" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A326" s="8" t="s">
+      <c r="A326" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B326" s="2" t="s">
@@ -14800,7 +14782,7 @@
       </c>
     </row>
     <row r="327" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A327" s="8" t="s">
+      <c r="A327" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B327" s="3" t="s">
@@ -14825,8 +14807,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="328" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A328" s="8" t="s">
+    <row r="328" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A328" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B328" s="2" t="s">
@@ -14851,8 +14833,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="329" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A329" s="8" t="s">
+    <row r="329" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A329" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B329" s="3" t="s">
@@ -14878,7 +14860,7 @@
       </c>
     </row>
     <row r="330" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A330" s="8" t="s">
+      <c r="A330" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B330" s="2" t="s">
@@ -14904,7 +14886,7 @@
       </c>
     </row>
     <row r="331" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A331" s="8" t="s">
+      <c r="A331" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B331" s="3" t="s">
@@ -14930,7 +14912,7 @@
       </c>
     </row>
     <row r="332" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A332" s="8" t="s">
+      <c r="A332" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B332" s="2" t="s">
@@ -14956,7 +14938,7 @@
       </c>
     </row>
     <row r="333" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A333" s="8" t="s">
+      <c r="A333" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B333" s="3" t="s">
@@ -14982,7 +14964,7 @@
       </c>
     </row>
     <row r="334" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A334" s="8" t="s">
+      <c r="A334" s="6" t="s">
         <v>798</v>
       </c>
       <c r="B334" s="2" t="s">
@@ -15008,7 +14990,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A335" s="8" t="s">
+      <c r="A335" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B335" s="3" t="s">
@@ -15034,7 +15016,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A336" s="8" t="s">
+      <c r="A336" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B336" s="2" t="s">
@@ -15060,7 +15042,7 @@
       </c>
     </row>
     <row r="337" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A337" s="8" t="s">
+      <c r="A337" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B337" s="3" t="s">
@@ -15086,7 +15068,7 @@
       </c>
     </row>
     <row r="338" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A338" s="8" t="s">
+      <c r="A338" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B338" s="2" t="s">
@@ -15112,7 +15094,7 @@
       </c>
     </row>
     <row r="339" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A339" s="8" t="s">
+      <c r="A339" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B339" s="3" t="s">
@@ -15138,7 +15120,7 @@
       </c>
     </row>
     <row r="340" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A340" s="8" t="s">
+      <c r="A340" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B340" s="2" t="s">
@@ -15164,7 +15146,7 @@
       </c>
     </row>
     <row r="341" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A341" s="8" t="s">
+      <c r="A341" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B341" s="3" t="s">
@@ -15190,7 +15172,7 @@
       </c>
     </row>
     <row r="342" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A342" s="8" t="s">
+      <c r="A342" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B342" s="2" t="s">
@@ -15216,7 +15198,7 @@
       </c>
     </row>
     <row r="343" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A343" s="8" t="s">
+      <c r="A343" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B343" s="3" t="s">
@@ -15242,7 +15224,7 @@
       </c>
     </row>
     <row r="344" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A344" s="8" t="s">
+      <c r="A344" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B344" s="2" t="s">
@@ -15268,7 +15250,7 @@
       </c>
     </row>
     <row r="345" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A345" s="8" t="s">
+      <c r="A345" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B345" s="3" t="s">
@@ -15293,8 +15275,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A346" s="8" t="s">
+    <row r="346" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A346" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B346" s="2" t="s">
@@ -15319,8 +15301,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="347" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A347" s="8" t="s">
+    <row r="347" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A347" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B347" s="3" t="s">
@@ -15346,7 +15328,7 @@
       </c>
     </row>
     <row r="348" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A348" s="8" t="s">
+      <c r="A348" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B348" s="2" t="s">
@@ -15372,7 +15354,7 @@
       </c>
     </row>
     <row r="349" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A349" s="8" t="s">
+      <c r="A349" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B349" s="3" t="s">
@@ -15398,7 +15380,7 @@
       </c>
     </row>
     <row r="350" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A350" s="8" t="s">
+      <c r="A350" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B350" s="2" t="s">
@@ -15424,7 +15406,7 @@
       </c>
     </row>
     <row r="351" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A351" s="8" t="s">
+      <c r="A351" s="6" t="s">
         <v>833</v>
       </c>
       <c r="B351" s="3" t="s">
@@ -15450,7 +15432,7 @@
       </c>
     </row>
     <row r="352" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A352" s="8" t="s">
+      <c r="A352" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B352" s="2" t="s">
@@ -15475,8 +15457,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A353" s="8" t="s">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A353" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B353" s="3" t="s">
@@ -15501,8 +15483,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="354" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A354" s="8" t="s">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A354" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B354" s="2" t="s">
@@ -15527,8 +15509,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="355" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A355" s="8" t="s">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A355" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B355" s="3" t="s">
@@ -15553,8 +15535,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="356" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A356" s="8" t="s">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A356" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B356" s="2" t="s">
@@ -15579,8 +15561,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="357" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A357" s="8" t="s">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A357" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B357" s="3" t="s">
@@ -15605,8 +15587,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="358" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A358" s="8" t="s">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A358" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B358" s="2" t="s">
@@ -15631,8 +15613,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="359" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A359" s="8" t="s">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A359" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B359" s="3" t="s">
@@ -15657,8 +15639,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="360" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A360" s="8" t="s">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A360" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B360" s="2" t="s">
@@ -15683,8 +15665,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="361" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A361" s="8" t="s">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A361" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B361" s="3" t="s">
@@ -15709,8 +15691,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="362" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A362" s="8" t="s">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A362" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B362" s="2" t="s">
@@ -15735,8 +15717,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="363" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A363" s="8" t="s">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A363" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B363" s="3" t="s">
@@ -15761,8 +15743,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="364" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A364" s="8" t="s">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A364" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B364" s="2" t="s">
@@ -15787,8 +15769,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="365" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A365" s="8" t="s">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A365" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B365" s="3" t="s">
@@ -15813,8 +15795,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="366" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A366" s="8" t="s">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A366" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B366" s="2" t="s">
@@ -15839,8 +15821,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="367" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A367" s="8" t="s">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A367" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B367" s="3" t="s">
@@ -15866,7 +15848,7 @@
       </c>
     </row>
     <row r="368" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A368" s="8" t="s">
+      <c r="A368" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B368" s="2" t="s">
@@ -15892,7 +15874,7 @@
       </c>
     </row>
     <row r="369" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A369" s="8" t="s">
+      <c r="A369" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B369" s="3" t="s">
@@ -15918,7 +15900,7 @@
       </c>
     </row>
     <row r="370" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A370" s="8" t="s">
+      <c r="A370" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B370" s="2" t="s">
@@ -15944,7 +15926,7 @@
       </c>
     </row>
     <row r="371" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A371" s="8" t="s">
+      <c r="A371" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B371" s="3" t="s">
@@ -15970,7 +15952,7 @@
       </c>
     </row>
     <row r="372" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A372" s="8" t="s">
+      <c r="A372" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B372" s="2" t="s">
@@ -15996,7 +15978,7 @@
       </c>
     </row>
     <row r="373" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A373" s="8" t="s">
+      <c r="A373" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B373" s="3" t="s">
@@ -16022,7 +16004,7 @@
       </c>
     </row>
     <row r="374" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A374" s="8" t="s">
+      <c r="A374" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B374" s="2" t="s">
@@ -16048,7 +16030,7 @@
       </c>
     </row>
     <row r="375" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A375" s="8" t="s">
+      <c r="A375" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B375" s="3" t="s">
@@ -16074,7 +16056,7 @@
       </c>
     </row>
     <row r="376" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A376" s="8" t="s">
+      <c r="A376" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B376" s="2" t="s">
@@ -16100,7 +16082,7 @@
       </c>
     </row>
     <row r="377" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A377" s="8" t="s">
+      <c r="A377" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B377" s="3" t="s">
@@ -16125,8 +16107,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A378" s="8" t="s">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A378" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B378" s="2" t="s">
@@ -16151,8 +16133,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="379" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A379" s="8" t="s">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A379" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B379" s="3" t="s">
@@ -16177,8 +16159,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="380" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A380" s="8" t="s">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A380" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B380" s="2" t="s">
@@ -16203,8 +16185,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="381" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A381" s="8" t="s">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A381" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B381" s="3" t="s">
@@ -16229,8 +16211,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="382" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A382" s="8" t="s">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A382" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B382" s="2" t="s">
@@ -16255,8 +16237,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="383" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A383" s="8" t="s">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A383" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B383" s="3" t="s">
@@ -16281,8 +16263,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A384" s="8" t="s">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A384" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B384" s="2" t="s">
@@ -16307,8 +16289,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A385" s="8" t="s">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A385" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B385" s="3" t="s">
@@ -16333,8 +16315,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A386" s="8" t="s">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A386" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B386" s="2" t="s">
@@ -16359,8 +16341,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="387" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A387" s="8" t="s">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A387" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B387" s="3" t="s">
@@ -16385,8 +16367,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A388" s="8" t="s">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A388" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B388" s="2" t="s">
@@ -16411,8 +16393,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="389" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A389" s="8" t="s">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A389" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B389" s="3" t="s">
@@ -16437,8 +16419,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="390" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A390" s="8" t="s">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A390" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B390" s="2" t="s">
@@ -16463,8 +16445,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="391" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A391" s="8" t="s">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A391" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B391" s="3" t="s">
@@ -16489,8 +16471,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="392" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A392" s="8" t="s">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A392" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B392" s="2" t="s">
@@ -16515,8 +16497,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="393" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A393" s="8" t="s">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A393" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B393" s="3" t="s">
@@ -16541,8 +16523,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="394" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A394" s="8" t="s">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A394" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B394" s="2" t="s">
@@ -16567,8 +16549,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="395" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A395" s="8" t="s">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A395" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B395" s="3" t="s">
@@ -16593,8 +16575,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="396" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A396" s="8" t="s">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A396" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B396" s="2" t="s">
@@ -16619,8 +16601,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="397" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A397" s="8" t="s">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A397" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B397" s="3" t="s">
@@ -16645,8 +16627,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="398" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A398" s="8" t="s">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A398" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B398" s="2" t="s">
@@ -16671,8 +16653,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="399" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A399" s="8" t="s">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A399" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B399" s="3" t="s">
@@ -16697,8 +16679,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="400" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A400" s="8" t="s">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A400" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B400" s="2" t="s">
@@ -16723,8 +16705,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="401" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A401" s="8" t="s">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A401" s="6" t="s">
         <v>865</v>
       </c>
       <c r="B401" s="3" t="s">
@@ -16750,7 +16732,7 @@
       </c>
     </row>
     <row r="402" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A402" s="8" t="s">
+      <c r="A402" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B402" s="2" t="s">
@@ -16776,7 +16758,7 @@
       </c>
     </row>
     <row r="403" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A403" s="8" t="s">
+      <c r="A403" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B403" s="3" t="s">
@@ -16802,7 +16784,7 @@
       </c>
     </row>
     <row r="404" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A404" s="8" t="s">
+      <c r="A404" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B404" s="2" t="s">
@@ -16828,7 +16810,7 @@
       </c>
     </row>
     <row r="405" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A405" s="8" t="s">
+      <c r="A405" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B405" s="3" t="s">
@@ -16854,7 +16836,7 @@
       </c>
     </row>
     <row r="406" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A406" s="8" t="s">
+      <c r="A406" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B406" s="2" t="s">
@@ -16880,7 +16862,7 @@
       </c>
     </row>
     <row r="407" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A407" s="8" t="s">
+      <c r="A407" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B407" s="3" t="s">
@@ -16906,7 +16888,7 @@
       </c>
     </row>
     <row r="408" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A408" s="8" t="s">
+      <c r="A408" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B408" s="2" t="s">
@@ -16932,7 +16914,7 @@
       </c>
     </row>
     <row r="409" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A409" s="8" t="s">
+      <c r="A409" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B409" s="3" t="s">
@@ -16958,7 +16940,7 @@
       </c>
     </row>
     <row r="410" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A410" s="8" t="s">
+      <c r="A410" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B410" s="2" t="s">
@@ -16984,7 +16966,7 @@
       </c>
     </row>
     <row r="411" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A411" s="8" t="s">
+      <c r="A411" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B411" s="3" t="s">
@@ -17010,7 +16992,7 @@
       </c>
     </row>
     <row r="412" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A412" s="8" t="s">
+      <c r="A412" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B412" s="2" t="s">
@@ -17036,7 +17018,7 @@
       </c>
     </row>
     <row r="413" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A413" s="8" t="s">
+      <c r="A413" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B413" s="3" t="s">
@@ -17062,7 +17044,7 @@
       </c>
     </row>
     <row r="414" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A414" s="8" t="s">
+      <c r="A414" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B414" s="2" t="s">
@@ -17088,7 +17070,7 @@
       </c>
     </row>
     <row r="415" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A415" s="8" t="s">
+      <c r="A415" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B415" s="3" t="s">
@@ -17114,7 +17096,7 @@
       </c>
     </row>
     <row r="416" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A416" s="8" t="s">
+      <c r="A416" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B416" s="2" t="s">
@@ -17140,7 +17122,7 @@
       </c>
     </row>
     <row r="417" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A417" s="8" t="s">
+      <c r="A417" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B417" s="3" t="s">
@@ -17166,7 +17148,7 @@
       </c>
     </row>
     <row r="418" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A418" s="8" t="s">
+      <c r="A418" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B418" s="2" t="s">
@@ -17192,7 +17174,7 @@
       </c>
     </row>
     <row r="419" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A419" s="8" t="s">
+      <c r="A419" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B419" s="3" t="s">
@@ -17218,7 +17200,7 @@
       </c>
     </row>
     <row r="420" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A420" s="8" t="s">
+      <c r="A420" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B420" s="2" t="s">
@@ -17244,7 +17226,7 @@
       </c>
     </row>
     <row r="421" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A421" s="8" t="s">
+      <c r="A421" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B421" s="3" t="s">
@@ -17270,7 +17252,7 @@
       </c>
     </row>
     <row r="422" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A422" s="8" t="s">
+      <c r="A422" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B422" s="2" t="s">
@@ -17296,7 +17278,7 @@
       </c>
     </row>
     <row r="423" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A423" s="8" t="s">
+      <c r="A423" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B423" s="3" t="s">
@@ -17322,7 +17304,7 @@
       </c>
     </row>
     <row r="424" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A424" s="8" t="s">
+      <c r="A424" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B424" s="2" t="s">
@@ -17347,8 +17329,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A425" s="8" t="s">
+    <row r="425" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A425" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B425" s="3" t="s">
@@ -17374,7 +17356,7 @@
       </c>
     </row>
     <row r="426" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A426" s="8" t="s">
+      <c r="A426" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B426" s="2" t="s">
@@ -17400,7 +17382,7 @@
       </c>
     </row>
     <row r="427" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A427" s="8" t="s">
+      <c r="A427" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B427" s="3" t="s">
@@ -17426,7 +17408,7 @@
       </c>
     </row>
     <row r="428" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A428" s="8" t="s">
+      <c r="A428" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B428" s="2" t="s">
@@ -17452,7 +17434,7 @@
       </c>
     </row>
     <row r="429" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A429" s="8" t="s">
+      <c r="A429" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B429" s="3" t="s">
@@ -17478,7 +17460,7 @@
       </c>
     </row>
     <row r="430" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A430" s="8" t="s">
+      <c r="A430" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B430" s="2" t="s">
@@ -17504,7 +17486,7 @@
       </c>
     </row>
     <row r="431" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A431" s="8" t="s">
+      <c r="A431" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B431" s="3" t="s">
@@ -17530,7 +17512,7 @@
       </c>
     </row>
     <row r="432" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A432" s="8" t="s">
+      <c r="A432" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B432" s="2" t="s">
@@ -17556,7 +17538,7 @@
       </c>
     </row>
     <row r="433" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A433" s="8" t="s">
+      <c r="A433" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B433" s="3" t="s">
@@ -17582,7 +17564,7 @@
       </c>
     </row>
     <row r="434" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A434" s="8" t="s">
+      <c r="A434" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B434" s="2" t="s">
@@ -17608,7 +17590,7 @@
       </c>
     </row>
     <row r="435" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A435" s="8" t="s">
+      <c r="A435" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B435" s="3" t="s">
@@ -17634,7 +17616,7 @@
       </c>
     </row>
     <row r="436" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A436" s="8" t="s">
+      <c r="A436" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B436" s="2" t="s">
@@ -17660,7 +17642,7 @@
       </c>
     </row>
     <row r="437" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A437" s="8" t="s">
+      <c r="A437" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B437" s="3" t="s">
@@ -17686,7 +17668,7 @@
       </c>
     </row>
     <row r="438" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A438" s="8" t="s">
+      <c r="A438" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B438" s="2" t="s">
@@ -17712,7 +17694,7 @@
       </c>
     </row>
     <row r="439" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A439" s="8" t="s">
+      <c r="A439" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B439" s="3" t="s">
@@ -17738,7 +17720,7 @@
       </c>
     </row>
     <row r="440" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A440" s="8" t="s">
+      <c r="A440" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B440" s="2" t="s">
@@ -17764,7 +17746,7 @@
       </c>
     </row>
     <row r="441" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A441" s="8" t="s">
+      <c r="A441" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B441" s="3" t="s">
@@ -17790,7 +17772,7 @@
       </c>
     </row>
     <row r="442" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A442" s="8" t="s">
+      <c r="A442" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B442" s="2" t="s">
@@ -17816,7 +17798,7 @@
       </c>
     </row>
     <row r="443" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A443" s="8" t="s">
+      <c r="A443" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B443" s="3" t="s">
@@ -17842,7 +17824,7 @@
       </c>
     </row>
     <row r="444" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A444" s="8" t="s">
+      <c r="A444" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B444" s="2" t="s">
@@ -17868,7 +17850,7 @@
       </c>
     </row>
     <row r="445" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A445" s="8" t="s">
+      <c r="A445" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B445" s="3" t="s">
@@ -17894,7 +17876,7 @@
       </c>
     </row>
     <row r="446" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A446" s="8" t="s">
+      <c r="A446" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B446" s="2" t="s">
@@ -17920,7 +17902,7 @@
       </c>
     </row>
     <row r="447" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A447" s="8" t="s">
+      <c r="A447" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B447" s="3" t="s">
@@ -17946,7 +17928,7 @@
       </c>
     </row>
     <row r="448" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A448" s="8" t="s">
+      <c r="A448" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B448" s="2" t="s">
@@ -17972,7 +17954,7 @@
       </c>
     </row>
     <row r="449" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A449" s="8" t="s">
+      <c r="A449" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B449" s="3" t="s">
@@ -17998,7 +17980,7 @@
       </c>
     </row>
     <row r="450" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A450" s="8" t="s">
+      <c r="A450" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B450" s="2" t="s">
@@ -18024,7 +18006,7 @@
       </c>
     </row>
     <row r="451" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A451" s="8" t="s">
+      <c r="A451" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B451" s="3" t="s">
@@ -18050,7 +18032,7 @@
       </c>
     </row>
     <row r="452" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A452" s="8" t="s">
+      <c r="A452" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B452" s="2" t="s">
@@ -18076,7 +18058,7 @@
       </c>
     </row>
     <row r="453" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A453" s="8" t="s">
+      <c r="A453" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B453" s="3" t="s">
@@ -18102,7 +18084,7 @@
       </c>
     </row>
     <row r="454" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A454" s="8" t="s">
+      <c r="A454" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B454" s="2" t="s">
@@ -18128,7 +18110,7 @@
       </c>
     </row>
     <row r="455" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A455" s="8" t="s">
+      <c r="A455" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B455" s="3" t="s">
@@ -18154,7 +18136,7 @@
       </c>
     </row>
     <row r="456" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A456" s="8" t="s">
+      <c r="A456" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B456" s="2" t="s">
@@ -18180,7 +18162,7 @@
       </c>
     </row>
     <row r="457" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A457" s="8" t="s">
+      <c r="A457" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B457" s="3" t="s">
@@ -18206,7 +18188,7 @@
       </c>
     </row>
     <row r="458" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A458" s="8" t="s">
+      <c r="A458" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B458" s="2" t="s">
@@ -18232,7 +18214,7 @@
       </c>
     </row>
     <row r="459" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A459" s="8" t="s">
+      <c r="A459" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B459" s="3" t="s">
@@ -18258,7 +18240,7 @@
       </c>
     </row>
     <row r="460" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A460" s="8" t="s">
+      <c r="A460" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B460" s="2" t="s">
@@ -18284,7 +18266,7 @@
       </c>
     </row>
     <row r="461" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A461" s="8" t="s">
+      <c r="A461" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B461" s="3" t="s">
@@ -18310,7 +18292,7 @@
       </c>
     </row>
     <row r="462" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A462" s="8" t="s">
+      <c r="A462" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B462" s="2" t="s">
@@ -18336,7 +18318,7 @@
       </c>
     </row>
     <row r="463" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A463" s="8" t="s">
+      <c r="A463" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B463" s="3" t="s">
@@ -18362,7 +18344,7 @@
       </c>
     </row>
     <row r="464" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A464" s="8" t="s">
+      <c r="A464" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B464" s="2" t="s">
@@ -18388,7 +18370,7 @@
       </c>
     </row>
     <row r="465" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A465" s="8" t="s">
+      <c r="A465" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B465" s="3" t="s">
@@ -18414,7 +18396,7 @@
       </c>
     </row>
     <row r="466" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A466" s="8" t="s">
+      <c r="A466" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B466" s="2" t="s">
@@ -18440,7 +18422,7 @@
       </c>
     </row>
     <row r="467" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A467" s="8" t="s">
+      <c r="A467" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B467" s="3" t="s">
@@ -18466,7 +18448,7 @@
       </c>
     </row>
     <row r="468" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A468" s="8" t="s">
+      <c r="A468" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B468" s="2" t="s">
@@ -18492,7 +18474,7 @@
       </c>
     </row>
     <row r="469" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A469" s="8" t="s">
+      <c r="A469" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B469" s="3" t="s">
@@ -18518,7 +18500,7 @@
       </c>
     </row>
     <row r="470" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A470" s="8" t="s">
+      <c r="A470" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B470" s="2" t="s">
@@ -18544,7 +18526,7 @@
       </c>
     </row>
     <row r="471" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A471" s="8" t="s">
+      <c r="A471" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B471" s="3" t="s">
@@ -18570,7 +18552,7 @@
       </c>
     </row>
     <row r="472" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A472" s="8" t="s">
+      <c r="A472" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B472" s="2" t="s">
@@ -18596,7 +18578,7 @@
       </c>
     </row>
     <row r="473" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A473" s="8" t="s">
+      <c r="A473" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B473" s="3" t="s">
@@ -18622,7 +18604,7 @@
       </c>
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A474" s="8" t="s">
+      <c r="A474" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B474" s="2" t="s">
@@ -18648,7 +18630,7 @@
       </c>
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A475" s="8" t="s">
+      <c r="A475" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B475" s="3" t="s">
@@ -18674,7 +18656,7 @@
       </c>
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A476" s="8" t="s">
+      <c r="A476" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B476" s="2" t="s">
@@ -18700,7 +18682,7 @@
       </c>
     </row>
     <row r="477" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A477" s="8" t="s">
+      <c r="A477" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B477" s="3" t="s">
@@ -18726,7 +18708,7 @@
       </c>
     </row>
     <row r="478" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A478" s="8" t="s">
+      <c r="A478" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B478" s="2" t="s">
@@ -18752,7 +18734,7 @@
       </c>
     </row>
     <row r="479" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A479" s="8" t="s">
+      <c r="A479" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B479" s="3" t="s">
@@ -18778,7 +18760,7 @@
       </c>
     </row>
     <row r="480" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A480" s="8" t="s">
+      <c r="A480" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B480" s="2" t="s">
@@ -18804,7 +18786,7 @@
       </c>
     </row>
     <row r="481" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A481" s="8" t="s">
+      <c r="A481" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B481" s="3" t="s">
@@ -18830,7 +18812,7 @@
       </c>
     </row>
     <row r="482" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A482" s="8" t="s">
+      <c r="A482" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B482" s="2" t="s">
@@ -18856,7 +18838,7 @@
       </c>
     </row>
     <row r="483" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A483" s="8" t="s">
+      <c r="A483" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B483" s="3" t="s">
@@ -18882,7 +18864,7 @@
       </c>
     </row>
     <row r="484" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A484" s="8" t="s">
+      <c r="A484" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B484" s="2" t="s">
@@ -18908,7 +18890,7 @@
       </c>
     </row>
     <row r="485" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A485" s="8" t="s">
+      <c r="A485" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B485" s="3" t="s">
@@ -18934,7 +18916,7 @@
       </c>
     </row>
     <row r="486" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A486" s="8" t="s">
+      <c r="A486" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B486" s="2" t="s">
@@ -18960,7 +18942,7 @@
       </c>
     </row>
     <row r="487" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A487" s="8" t="s">
+      <c r="A487" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B487" s="3" t="s">
@@ -18986,7 +18968,7 @@
       </c>
     </row>
     <row r="488" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A488" s="8" t="s">
+      <c r="A488" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B488" s="2" t="s">
@@ -19012,7 +18994,7 @@
       </c>
     </row>
     <row r="489" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A489" s="8" t="s">
+      <c r="A489" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B489" s="3" t="s">
@@ -19038,7 +19020,7 @@
       </c>
     </row>
     <row r="490" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A490" s="8" t="s">
+      <c r="A490" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B490" s="2" t="s">
@@ -19064,7 +19046,7 @@
       </c>
     </row>
     <row r="491" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A491" s="8" t="s">
+      <c r="A491" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B491" s="3" t="s">
@@ -19090,7 +19072,7 @@
       </c>
     </row>
     <row r="492" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A492" s="8" t="s">
+      <c r="A492" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B492" s="2" t="s">
@@ -19116,7 +19098,7 @@
       </c>
     </row>
     <row r="493" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A493" s="8" t="s">
+      <c r="A493" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B493" s="3" t="s">
@@ -19142,7 +19124,7 @@
       </c>
     </row>
     <row r="494" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A494" s="8" t="s">
+      <c r="A494" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B494" s="2" t="s">
@@ -19168,7 +19150,7 @@
       </c>
     </row>
     <row r="495" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A495" s="8" t="s">
+      <c r="A495" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B495" s="3" t="s">
@@ -19194,7 +19176,7 @@
       </c>
     </row>
     <row r="496" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A496" s="8" t="s">
+      <c r="A496" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B496" s="2" t="s">
@@ -19220,7 +19202,7 @@
       </c>
     </row>
     <row r="497" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A497" s="8" t="s">
+      <c r="A497" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B497" s="3" t="s">
@@ -19246,7 +19228,7 @@
       </c>
     </row>
     <row r="498" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A498" s="8" t="s">
+      <c r="A498" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B498" s="2" t="s">
@@ -19272,7 +19254,7 @@
       </c>
     </row>
     <row r="499" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A499" s="8" t="s">
+      <c r="A499" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B499" s="3" t="s">
@@ -19298,7 +19280,7 @@
       </c>
     </row>
     <row r="500" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A500" s="8" t="s">
+      <c r="A500" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B500" s="2" t="s">
@@ -19324,7 +19306,7 @@
       </c>
     </row>
     <row r="501" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A501" s="8" t="s">
+      <c r="A501" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B501" s="3" t="s">
@@ -19350,7 +19332,7 @@
       </c>
     </row>
     <row r="502" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A502" s="8" t="s">
+      <c r="A502" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B502" s="2" t="s">
@@ -19376,7 +19358,7 @@
       </c>
     </row>
     <row r="503" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A503" s="8" t="s">
+      <c r="A503" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B503" s="3" t="s">
@@ -19402,7 +19384,7 @@
       </c>
     </row>
     <row r="504" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A504" s="8" t="s">
+      <c r="A504" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B504" s="2" t="s">
@@ -19428,7 +19410,7 @@
       </c>
     </row>
     <row r="505" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A505" s="8" t="s">
+      <c r="A505" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B505" s="3" t="s">
@@ -19454,7 +19436,7 @@
       </c>
     </row>
     <row r="506" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A506" s="8" t="s">
+      <c r="A506" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B506" s="2" t="s">
@@ -19480,7 +19462,7 @@
       </c>
     </row>
     <row r="507" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A507" s="8" t="s">
+      <c r="A507" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B507" s="3" t="s">
@@ -19506,7 +19488,7 @@
       </c>
     </row>
     <row r="508" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A508" s="8" t="s">
+      <c r="A508" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B508" s="2" t="s">
@@ -19532,7 +19514,7 @@
       </c>
     </row>
     <row r="509" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A509" s="8" t="s">
+      <c r="A509" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B509" s="3" t="s">
@@ -19558,7 +19540,7 @@
       </c>
     </row>
     <row r="510" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A510" s="8" t="s">
+      <c r="A510" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B510" s="2" t="s">
@@ -19584,7 +19566,7 @@
       </c>
     </row>
     <row r="511" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A511" s="8" t="s">
+      <c r="A511" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B511" s="3" t="s">
@@ -19609,8 +19591,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="512" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A512" s="8" t="s">
+    <row r="512" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A512" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B512" s="2" t="s">
@@ -19635,8 +19617,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="513" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A513" s="8" t="s">
+    <row r="513" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A513" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B513" s="3" t="s">
@@ -19662,7 +19644,7 @@
       </c>
     </row>
     <row r="514" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A514" s="8" t="s">
+      <c r="A514" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B514" s="2" t="s">
@@ -19688,7 +19670,7 @@
       </c>
     </row>
     <row r="515" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A515" s="8" t="s">
+      <c r="A515" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B515" s="3" t="s">
@@ -19714,7 +19696,7 @@
       </c>
     </row>
     <row r="516" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A516" s="8" t="s">
+      <c r="A516" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B516" s="2" t="s">
@@ -19739,8 +19721,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="517" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A517" s="8" t="s">
+    <row r="517" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A517" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B517" s="3" t="s">
@@ -19765,8 +19747,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="518" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A518" s="8" t="s">
+    <row r="518" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A518" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B518" s="2" t="s">
@@ -19792,7 +19774,7 @@
       </c>
     </row>
     <row r="519" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A519" s="8" t="s">
+      <c r="A519" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B519" s="3" t="s">
@@ -19818,7 +19800,7 @@
       </c>
     </row>
     <row r="520" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A520" s="8" t="s">
+      <c r="A520" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B520" s="2" t="s">
@@ -19844,7 +19826,7 @@
       </c>
     </row>
     <row r="521" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A521" s="8" t="s">
+      <c r="A521" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B521" s="3" t="s">
@@ -19870,7 +19852,7 @@
       </c>
     </row>
     <row r="522" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A522" s="8" t="s">
+      <c r="A522" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B522" s="2" t="s">
@@ -19896,7 +19878,7 @@
       </c>
     </row>
     <row r="523" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A523" s="8" t="s">
+      <c r="A523" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B523" s="3" t="s">
@@ -19922,7 +19904,7 @@
       </c>
     </row>
     <row r="524" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A524" s="8" t="s">
+      <c r="A524" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B524" s="2" t="s">
@@ -19948,7 +19930,7 @@
       </c>
     </row>
     <row r="525" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A525" s="8" t="s">
+      <c r="A525" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B525" s="3" t="s">
@@ -19974,7 +19956,7 @@
       </c>
     </row>
     <row r="526" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A526" s="8" t="s">
+      <c r="A526" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B526" s="2" t="s">
@@ -20000,7 +19982,7 @@
       </c>
     </row>
     <row r="527" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A527" s="8" t="s">
+      <c r="A527" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B527" s="3" t="s">
@@ -20026,7 +20008,7 @@
       </c>
     </row>
     <row r="528" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A528" s="8" t="s">
+      <c r="A528" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B528" s="2" t="s">
@@ -20052,7 +20034,7 @@
       </c>
     </row>
     <row r="529" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A529" s="8" t="s">
+      <c r="A529" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B529" s="3" t="s">
@@ -20078,7 +20060,7 @@
       </c>
     </row>
     <row r="530" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A530" s="8" t="s">
+      <c r="A530" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B530" s="2" t="s">
@@ -20104,7 +20086,7 @@
       </c>
     </row>
     <row r="531" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A531" s="8" t="s">
+      <c r="A531" s="6" t="s">
         <v>984</v>
       </c>
       <c r="B531" s="3" t="s">
@@ -20130,7 +20112,7 @@
       </c>
     </row>
     <row r="532" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A532" s="8" t="s">
+      <c r="A532" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B532" s="2" t="s">
@@ -20156,7 +20138,7 @@
       </c>
     </row>
     <row r="533" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A533" s="8" t="s">
+      <c r="A533" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B533" s="3" t="s">
@@ -20182,7 +20164,7 @@
       </c>
     </row>
     <row r="534" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A534" s="8" t="s">
+      <c r="A534" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B534" s="2" t="s">
@@ -20208,7 +20190,7 @@
       </c>
     </row>
     <row r="535" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A535" s="8" t="s">
+      <c r="A535" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B535" s="3" t="s">
@@ -20234,7 +20216,7 @@
       </c>
     </row>
     <row r="536" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A536" s="8" t="s">
+      <c r="A536" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B536" s="2" t="s">
@@ -20260,7 +20242,7 @@
       </c>
     </row>
     <row r="537" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A537" s="8" t="s">
+      <c r="A537" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B537" s="3" t="s">
@@ -20286,7 +20268,7 @@
       </c>
     </row>
     <row r="538" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A538" s="8" t="s">
+      <c r="A538" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B538" s="2" t="s">
@@ -20312,7 +20294,7 @@
       </c>
     </row>
     <row r="539" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A539" s="8" t="s">
+      <c r="A539" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B539" s="3" t="s">
@@ -20338,7 +20320,7 @@
       </c>
     </row>
     <row r="540" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A540" s="8" t="s">
+      <c r="A540" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B540" s="2" t="s">
@@ -20364,7 +20346,7 @@
       </c>
     </row>
     <row r="541" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A541" s="8" t="s">
+      <c r="A541" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B541" s="3" t="s">
@@ -20390,7 +20372,7 @@
       </c>
     </row>
     <row r="542" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A542" s="8" t="s">
+      <c r="A542" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B542" s="2" t="s">
@@ -20416,7 +20398,7 @@
       </c>
     </row>
     <row r="543" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A543" s="8" t="s">
+      <c r="A543" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B543" s="3" t="s">
@@ -20442,7 +20424,7 @@
       </c>
     </row>
     <row r="544" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A544" s="8" t="s">
+      <c r="A544" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B544" s="2" t="s">
@@ -20468,7 +20450,7 @@
       </c>
     </row>
     <row r="545" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A545" s="8" t="s">
+      <c r="A545" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B545" s="3" t="s">
@@ -20494,7 +20476,7 @@
       </c>
     </row>
     <row r="546" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A546" s="8" t="s">
+      <c r="A546" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B546" s="2" t="s">
@@ -20520,7 +20502,7 @@
       </c>
     </row>
     <row r="547" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A547" s="8" t="s">
+      <c r="A547" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B547" s="3" t="s">
@@ -20546,7 +20528,7 @@
       </c>
     </row>
     <row r="548" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A548" s="8" t="s">
+      <c r="A548" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B548" s="2" t="s">
@@ -20572,7 +20554,7 @@
       </c>
     </row>
     <row r="549" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A549" s="8" t="s">
+      <c r="A549" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B549" s="3" t="s">
@@ -20598,7 +20580,7 @@
       </c>
     </row>
     <row r="550" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A550" s="8" t="s">
+      <c r="A550" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B550" s="2" t="s">
@@ -20624,7 +20606,7 @@
       </c>
     </row>
     <row r="551" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A551" s="8" t="s">
+      <c r="A551" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B551" s="3" t="s">
@@ -20650,7 +20632,7 @@
       </c>
     </row>
     <row r="552" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A552" s="8" t="s">
+      <c r="A552" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B552" s="2" t="s">
@@ -20676,7 +20658,7 @@
       </c>
     </row>
     <row r="553" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A553" s="8" t="s">
+      <c r="A553" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B553" s="3" t="s">
@@ -20702,7 +20684,7 @@
       </c>
     </row>
     <row r="554" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A554" s="8" t="s">
+      <c r="A554" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B554" s="2" t="s">
@@ -20728,7 +20710,7 @@
       </c>
     </row>
     <row r="555" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A555" s="8" t="s">
+      <c r="A555" s="6" t="s">
         <v>1276</v>
       </c>
       <c r="B555" s="3" t="s">
@@ -20754,7 +20736,7 @@
       </c>
     </row>
     <row r="556" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A556" s="8" t="s">
+      <c r="A556" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B556" s="2" t="s">
@@ -20780,7 +20762,7 @@
       </c>
     </row>
     <row r="557" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A557" s="8" t="s">
+      <c r="A557" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B557" s="3" t="s">
@@ -20806,7 +20788,7 @@
       </c>
     </row>
     <row r="558" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A558" s="8" t="s">
+      <c r="A558" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B558" s="2" t="s">
@@ -20832,7 +20814,7 @@
       </c>
     </row>
     <row r="559" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A559" s="8" t="s">
+      <c r="A559" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B559" s="3" t="s">
@@ -20858,7 +20840,7 @@
       </c>
     </row>
     <row r="560" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A560" s="8" t="s">
+      <c r="A560" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B560" s="2" t="s">
@@ -20884,7 +20866,7 @@
       </c>
     </row>
     <row r="561" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A561" s="8" t="s">
+      <c r="A561" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B561" s="3" t="s">
@@ -20910,7 +20892,7 @@
       </c>
     </row>
     <row r="562" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A562" s="8" t="s">
+      <c r="A562" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B562" s="2" t="s">
@@ -20936,7 +20918,7 @@
       </c>
     </row>
     <row r="563" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A563" s="8" t="s">
+      <c r="A563" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B563" s="3" t="s">
@@ -20962,7 +20944,7 @@
       </c>
     </row>
     <row r="564" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A564" s="8" t="s">
+      <c r="A564" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B564" s="2" t="s">
@@ -20988,7 +20970,7 @@
       </c>
     </row>
     <row r="565" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A565" s="8" t="s">
+      <c r="A565" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B565" s="3" t="s">
@@ -21014,7 +20996,7 @@
       </c>
     </row>
     <row r="566" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A566" s="8" t="s">
+      <c r="A566" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B566" s="2" t="s">
@@ -21040,7 +21022,7 @@
       </c>
     </row>
     <row r="567" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A567" s="8" t="s">
+      <c r="A567" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B567" s="3" t="s">
@@ -21065,8 +21047,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="568" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A568" s="8" t="s">
+    <row r="568" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A568" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B568" s="2" t="s">
@@ -21091,8 +21073,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="569" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A569" s="8" t="s">
+    <row r="569" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A569" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B569" s="3" t="s">
@@ -21118,7 +21100,7 @@
       </c>
     </row>
     <row r="570" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A570" s="8" t="s">
+      <c r="A570" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B570" s="2" t="s">
@@ -21144,7 +21126,7 @@
       </c>
     </row>
     <row r="571" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A571" s="8" t="s">
+      <c r="A571" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B571" s="3" t="s">
@@ -21170,7 +21152,7 @@
       </c>
     </row>
     <row r="572" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A572" s="8" t="s">
+      <c r="A572" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B572" s="2" t="s">
@@ -21195,8 +21177,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="573" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A573" s="8" t="s">
+    <row r="573" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A573" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B573" s="3" t="s">
@@ -21221,8 +21203,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="574" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A574" s="8" t="s">
+    <row r="574" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A574" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B574" s="2" t="s">
@@ -21248,7 +21230,7 @@
       </c>
     </row>
     <row r="575" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A575" s="8" t="s">
+      <c r="A575" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B575" s="3" t="s">
@@ -21274,7 +21256,7 @@
       </c>
     </row>
     <row r="576" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A576" s="8" t="s">
+      <c r="A576" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B576" s="2" t="s">
@@ -21300,7 +21282,7 @@
       </c>
     </row>
     <row r="577" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A577" s="8" t="s">
+      <c r="A577" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B577" s="3" t="s">
@@ -21326,7 +21308,7 @@
       </c>
     </row>
     <row r="578" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A578" s="8" t="s">
+      <c r="A578" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B578" s="2" t="s">
@@ -21352,7 +21334,7 @@
       </c>
     </row>
     <row r="579" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A579" s="8" t="s">
+      <c r="A579" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B579" s="3" t="s">
@@ -21378,7 +21360,7 @@
       </c>
     </row>
     <row r="580" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A580" s="8" t="s">
+      <c r="A580" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B580" s="2" t="s">
@@ -21404,7 +21386,7 @@
       </c>
     </row>
     <row r="581" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A581" s="8" t="s">
+      <c r="A581" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B581" s="3" t="s">
@@ -21430,7 +21412,7 @@
       </c>
     </row>
     <row r="582" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A582" s="8" t="s">
+      <c r="A582" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B582" s="2" t="s">
@@ -21456,7 +21438,7 @@
       </c>
     </row>
     <row r="583" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A583" s="8" t="s">
+      <c r="A583" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B583" s="3" t="s">
@@ -21482,7 +21464,7 @@
       </c>
     </row>
     <row r="584" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A584" s="8" t="s">
+      <c r="A584" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B584" s="2" t="s">
@@ -21508,7 +21490,7 @@
       </c>
     </row>
     <row r="585" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A585" s="8" t="s">
+      <c r="A585" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B585" s="3" t="s">
@@ -21534,7 +21516,7 @@
       </c>
     </row>
     <row r="586" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A586" s="8" t="s">
+      <c r="A586" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B586" s="2" t="s">
@@ -21560,7 +21542,7 @@
       </c>
     </row>
     <row r="587" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A587" s="8" t="s">
+      <c r="A587" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B587" s="3" t="s">
@@ -21586,7 +21568,7 @@
       </c>
     </row>
     <row r="588" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A588" s="8" t="s">
+      <c r="A588" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B588" s="2" t="s">
@@ -21612,7 +21594,7 @@
       </c>
     </row>
     <row r="589" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A589" s="8" t="s">
+      <c r="A589" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B589" s="3" t="s">
@@ -21638,7 +21620,7 @@
       </c>
     </row>
     <row r="590" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A590" s="8" t="s">
+      <c r="A590" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B590" s="2" t="s">
@@ -21664,7 +21646,7 @@
       </c>
     </row>
     <row r="591" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A591" s="8" t="s">
+      <c r="A591" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B591" s="3" t="s">
@@ -21690,7 +21672,7 @@
       </c>
     </row>
     <row r="592" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A592" s="8" t="s">
+      <c r="A592" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B592" s="2" t="s">
@@ -21716,7 +21698,7 @@
       </c>
     </row>
     <row r="593" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A593" s="8" t="s">
+      <c r="A593" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B593" s="3" t="s">
@@ -21742,7 +21724,7 @@
       </c>
     </row>
     <row r="594" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A594" s="8" t="s">
+      <c r="A594" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B594" s="2" t="s">
@@ -21768,7 +21750,7 @@
       </c>
     </row>
     <row r="595" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A595" s="8" t="s">
+      <c r="A595" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B595" s="3" t="s">
@@ -21794,7 +21776,7 @@
       </c>
     </row>
     <row r="596" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A596" s="8" t="s">
+      <c r="A596" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B596" s="2" t="s">
@@ -21820,7 +21802,7 @@
       </c>
     </row>
     <row r="597" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A597" s="8" t="s">
+      <c r="A597" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B597" s="3" t="s">
@@ -21846,7 +21828,7 @@
       </c>
     </row>
     <row r="598" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A598" s="8" t="s">
+      <c r="A598" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B598" s="2" t="s">
@@ -21872,7 +21854,7 @@
       </c>
     </row>
     <row r="599" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A599" s="8" t="s">
+      <c r="A599" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B599" s="3" t="s">
@@ -21898,7 +21880,7 @@
       </c>
     </row>
     <row r="600" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A600" s="8" t="s">
+      <c r="A600" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B600" s="2" t="s">
@@ -21924,7 +21906,7 @@
       </c>
     </row>
     <row r="601" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A601" s="8" t="s">
+      <c r="A601" s="6" t="s">
         <v>1338</v>
       </c>
       <c r="B601" s="3" t="s">
@@ -21950,7 +21932,7 @@
       </c>
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A602" s="8" t="s">
+      <c r="A602" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B602" s="2" t="s">
@@ -21976,7 +21958,7 @@
       </c>
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A603" s="8" t="s">
+      <c r="A603" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B603" s="3" t="s">
@@ -22002,7 +21984,7 @@
       </c>
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A604" s="8" t="s">
+      <c r="A604" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B604" s="2" t="s">
@@ -22028,7 +22010,7 @@
       </c>
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A605" s="8" t="s">
+      <c r="A605" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B605" s="3" t="s">
@@ -22054,7 +22036,7 @@
       </c>
     </row>
     <row r="606" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A606" s="8" t="s">
+      <c r="A606" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B606" s="2" t="s">
@@ -22080,7 +22062,7 @@
       </c>
     </row>
     <row r="607" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A607" s="8" t="s">
+      <c r="A607" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B607" s="3" t="s">
@@ -22105,8 +22087,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="608" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A608" s="8" t="s">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A608" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B608" s="2" t="s">
@@ -22132,7 +22114,7 @@
       </c>
     </row>
     <row r="609" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A609" s="8" t="s">
+      <c r="A609" s="6" t="s">
         <v>1454</v>
       </c>
       <c r="B609" s="3" t="s">
@@ -22158,7 +22140,7 @@
       </c>
     </row>
     <row r="610" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A610" s="8" t="s">
+      <c r="A610" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B610" s="2" t="s">
@@ -22183,8 +22165,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="611" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A611" s="8" t="s">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A611" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B611" s="3" t="s">
@@ -22210,7 +22192,7 @@
       </c>
     </row>
     <row r="612" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A612" s="8" t="s">
+      <c r="A612" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B612" s="2" t="s">
@@ -22236,7 +22218,7 @@
       </c>
     </row>
     <row r="613" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A613" s="8" t="s">
+      <c r="A613" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B613" s="3" t="s">
@@ -22261,8 +22243,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="614" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A614" s="8" t="s">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A614" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B614" s="2" t="s">
@@ -22287,8 +22269,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="615" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A615" s="8" t="s">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A615" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B615" s="3" t="s">
@@ -22313,8 +22295,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="616" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A616" s="8" t="s">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A616" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B616" s="2" t="s">
@@ -22339,8 +22321,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="617" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A617" s="8" t="s">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A617" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B617" s="3" t="s">
@@ -22365,8 +22347,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="618" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A618" s="8" t="s">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A618" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B618" s="2" t="s">
@@ -22391,8 +22373,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="619" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A619" s="8" t="s">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A619" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B619" s="3" t="s">
@@ -22417,8 +22399,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="620" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A620" s="8" t="s">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A620" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B620" s="2" t="s">
@@ -22443,8 +22425,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="621" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A621" s="8" t="s">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A621" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B621" s="3" t="s">
@@ -22469,8 +22451,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="622" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A622" s="8" t="s">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A622" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B622" s="2" t="s">
@@ -22495,8 +22477,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="623" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A623" s="8" t="s">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A623" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B623" s="3" t="s">
@@ -22521,8 +22503,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="624" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A624" s="8" t="s">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A624" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B624" s="2" t="s">
@@ -22547,8 +22529,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="625" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A625" s="8" t="s">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A625" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B625" s="3" t="s">
@@ -22573,8 +22555,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="626" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A626" s="8" t="s">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A626" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B626" s="2" t="s">
@@ -22599,8 +22581,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="627" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A627" s="8" t="s">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A627" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B627" s="3" t="s">
@@ -22625,8 +22607,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="628" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A628" s="8" t="s">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A628" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B628" s="2" t="s">
@@ -22651,8 +22633,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="629" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A629" s="8" t="s">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A629" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B629" s="3" t="s">
@@ -22677,8 +22659,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="630" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A630" s="8" t="s">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A630" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B630" s="2" t="s">
@@ -22703,8 +22685,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="631" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A631" s="8" t="s">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A631" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B631" s="3" t="s">
@@ -22729,8 +22711,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="632" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A632" s="8" t="s">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A632" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B632" s="2" t="s">
@@ -22755,8 +22737,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="633" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A633" s="8" t="s">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A633" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B633" s="3" t="s">
@@ -22781,8 +22763,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="634" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A634" s="8" t="s">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A634" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B634" s="2" t="s">
@@ -22807,8 +22789,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="635" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A635" s="8" t="s">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A635" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B635" s="3" t="s">
@@ -22833,8 +22815,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="636" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A636" s="8" t="s">
+    <row r="636" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A636" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B636" s="2" t="s">
@@ -22859,8 +22841,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="637" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A637" s="8" t="s">
+    <row r="637" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A637" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B637" s="3" t="s">
@@ -22885,8 +22867,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="638" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A638" s="8" t="s">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A638" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B638" s="2" t="s">
@@ -22911,8 +22893,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="639" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A639" s="8" t="s">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A639" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B639" s="3" t="s">
@@ -22938,7 +22920,7 @@
       </c>
     </row>
     <row r="640" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A640" s="8" t="s">
+      <c r="A640" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B640" s="2" t="s">
@@ -22963,8 +22945,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="641" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A641" s="8" t="s">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A641" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B641" s="3" t="s">
@@ -22989,8 +22971,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="642" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A642" s="8" t="s">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A642" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B642" s="2" t="s">
@@ -23015,8 +22997,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="643" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A643" s="8" t="s">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A643" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B643" s="3" t="s">
@@ -23041,8 +23023,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="644" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A644" s="8" t="s">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A644" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B644" s="2" t="s">
@@ -23067,8 +23049,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="645" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A645" s="8" t="s">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A645" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B645" s="3" t="s">
@@ -23093,8 +23075,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="646" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A646" s="8" t="s">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A646" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B646" s="2" t="s">
@@ -23119,8 +23101,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="647" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A647" s="8" t="s">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A647" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B647" s="3" t="s">
@@ -23145,8 +23127,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="648" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A648" s="8" t="s">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A648" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B648" s="2" t="s">
@@ -23171,8 +23153,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="649" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A649" s="8" t="s">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A649" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B649" s="3" t="s">
@@ -23198,7 +23180,7 @@
       </c>
     </row>
     <row r="650" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A650" s="8" t="s">
+      <c r="A650" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B650" s="2" t="s">
@@ -23223,8 +23205,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="651" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A651" s="8" t="s">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A651" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B651" s="3" t="s">
@@ -23250,7 +23232,7 @@
       </c>
     </row>
     <row r="652" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A652" s="8" t="s">
+      <c r="A652" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B652" s="2" t="s">
@@ -23276,7 +23258,7 @@
       </c>
     </row>
     <row r="653" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A653" s="8" t="s">
+      <c r="A653" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B653" s="3" t="s">
@@ -23301,8 +23283,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="654" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A654" s="8" t="s">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A654" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B654" s="2" t="s">
@@ -23327,8 +23309,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="655" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A655" s="8" t="s">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A655" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B655" s="3" t="s">
@@ -23353,8 +23335,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="656" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A656" s="8" t="s">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A656" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B656" s="2" t="s">
@@ -23379,8 +23361,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="657" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A657" s="8" t="s">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A657" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B657" s="3" t="s">
@@ -23405,8 +23387,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="658" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A658" s="8" t="s">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A658" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B658" s="2" t="s">
@@ -23431,8 +23413,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="659" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A659" s="8" t="s">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A659" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B659" s="3" t="s">
@@ -23457,8 +23439,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="660" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A660" s="8" t="s">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A660" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B660" s="2" t="s">
@@ -23483,8 +23465,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="661" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A661" s="8" t="s">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A661" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B661" s="3" t="s">
@@ -23510,7 +23492,7 @@
       </c>
     </row>
     <row r="662" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A662" s="8" t="s">
+      <c r="A662" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B662" s="2" t="s">
@@ -23536,7 +23518,7 @@
       </c>
     </row>
     <row r="663" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A663" s="8" t="s">
+      <c r="A663" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B663" s="3" t="s">
@@ -23562,7 +23544,7 @@
       </c>
     </row>
     <row r="664" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A664" s="8" t="s">
+      <c r="A664" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B664" s="2" t="s">
@@ -23588,7 +23570,7 @@
       </c>
     </row>
     <row r="665" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A665" s="8" t="s">
+      <c r="A665" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B665" s="3" t="s">
@@ -23614,7 +23596,7 @@
       </c>
     </row>
     <row r="666" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A666" s="8" t="s">
+      <c r="A666" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B666" s="2" t="s">
@@ -23639,8 +23621,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="667" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A667" s="8" t="s">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A667" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B667" s="3" t="s">
@@ -23665,8 +23647,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="668" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A668" s="8" t="s">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A668" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B668" s="2" t="s">
@@ -23692,7 +23674,7 @@
       </c>
     </row>
     <row r="669" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A669" s="8" t="s">
+      <c r="A669" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B669" s="3" t="s">
@@ -23718,7 +23700,7 @@
       </c>
     </row>
     <row r="670" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A670" s="8" t="s">
+      <c r="A670" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B670" s="2" t="s">
@@ -23744,7 +23726,7 @@
       </c>
     </row>
     <row r="671" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A671" s="8" t="s">
+      <c r="A671" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B671" s="3" t="s">
@@ -23770,7 +23752,7 @@
       </c>
     </row>
     <row r="672" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A672" s="8" t="s">
+      <c r="A672" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B672" s="2" t="s">
@@ -23796,7 +23778,7 @@
       </c>
     </row>
     <row r="673" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A673" s="8" t="s">
+      <c r="A673" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B673" s="3" t="s">
@@ -23822,7 +23804,7 @@
       </c>
     </row>
     <row r="674" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A674" s="8" t="s">
+      <c r="A674" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B674" s="2" t="s">
@@ -23848,7 +23830,7 @@
       </c>
     </row>
     <row r="675" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A675" s="8" t="s">
+      <c r="A675" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B675" s="3" t="s">
@@ -23873,8 +23855,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="676" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A676" s="8" t="s">
+    <row r="676" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A676" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B676" s="2" t="s">
@@ -23899,8 +23881,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="677" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A677" s="8" t="s">
+    <row r="677" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A677" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B677" s="3" t="s">
@@ -23925,8 +23907,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="678" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A678" s="8" t="s">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A678" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B678" s="2" t="s">
@@ -23951,8 +23933,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="679" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A679" s="8" t="s">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A679" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B679" s="3" t="s">
@@ -23978,7 +23960,7 @@
       </c>
     </row>
     <row r="680" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A680" s="8" t="s">
+      <c r="A680" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B680" s="2" t="s">
@@ -24003,8 +23985,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="681" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A681" s="8" t="s">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A681" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B681" s="3" t="s">
@@ -24029,8 +24011,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="682" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A682" s="8" t="s">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A682" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B682" s="2" t="s">
@@ -24055,8 +24037,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="683" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A683" s="8" t="s">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A683" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B683" s="3" t="s">
@@ -24081,8 +24063,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="684" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A684" s="8" t="s">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A684" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B684" s="2" t="s">
@@ -24107,8 +24089,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="685" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A685" s="8" t="s">
+    <row r="685" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A685" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B685" s="3" t="s">
@@ -24133,8 +24115,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="686" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A686" s="8" t="s">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A686" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B686" s="2" t="s">
@@ -24159,8 +24141,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="687" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A687" s="8" t="s">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A687" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B687" s="3" t="s">
@@ -24185,8 +24167,8 @@
         <v>795</v>
       </c>
     </row>
-    <row r="688" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A688" s="8" t="s">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A688" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B688" s="2" t="s">
@@ -24212,7 +24194,7 @@
       </c>
     </row>
     <row r="689" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A689" s="8" t="s">
+      <c r="A689" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B689" s="3" t="s">
@@ -24238,7 +24220,7 @@
       </c>
     </row>
     <row r="690" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A690" s="8" t="s">
+      <c r="A690" s="6" t="s">
         <v>1475</v>
       </c>
       <c r="B690" s="2" t="s">
@@ -24264,7 +24246,7 @@
       </c>
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A691" s="8" t="s">
+      <c r="A691" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B691" s="3" t="s">
@@ -24290,7 +24272,7 @@
       </c>
     </row>
     <row r="692" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A692" s="8" t="s">
+      <c r="A692" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B692" s="2" t="s">
@@ -24316,7 +24298,7 @@
       </c>
     </row>
     <row r="693" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A693" s="8" t="s">
+      <c r="A693" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B693" s="3" t="s">
@@ -24342,7 +24324,7 @@
       </c>
     </row>
     <row r="694" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A694" s="8" t="s">
+      <c r="A694" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B694" s="2" t="s">
@@ -24368,7 +24350,7 @@
       </c>
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A695" s="8" t="s">
+      <c r="A695" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B695" s="3" t="s">
@@ -24394,7 +24376,7 @@
       </c>
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A696" s="8" t="s">
+      <c r="A696" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B696" s="2" t="s">
@@ -24420,7 +24402,7 @@
       </c>
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A697" s="8" t="s">
+      <c r="A697" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B697" s="3" t="s">
@@ -24446,7 +24428,7 @@
       </c>
     </row>
     <row r="698" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A698" s="8" t="s">
+      <c r="A698" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B698" s="2" t="s">
@@ -24472,7 +24454,7 @@
       </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A699" s="8" t="s">
+      <c r="A699" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B699" s="3" t="s">
@@ -24498,7 +24480,7 @@
       </c>
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A700" s="8" t="s">
+      <c r="A700" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B700" s="2" t="s">
@@ -24524,7 +24506,7 @@
       </c>
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A701" s="8" t="s">
+      <c r="A701" s="6" t="s">
         <v>1646</v>
       </c>
       <c r="B701" s="3" t="s">
@@ -24550,7 +24532,7 @@
       </c>
     </row>
     <row r="702" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A702" s="8" t="s">
+      <c r="A702" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B702" s="2" t="s">
@@ -24576,7 +24558,7 @@
       </c>
     </row>
     <row r="703" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A703" s="8" t="s">
+      <c r="A703" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B703" s="3" t="s">
@@ -24602,7 +24584,7 @@
       </c>
     </row>
     <row r="704" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A704" s="8" t="s">
+      <c r="A704" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B704" s="2" t="s">
@@ -24628,7 +24610,7 @@
       </c>
     </row>
     <row r="705" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A705" s="8" t="s">
+      <c r="A705" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B705" s="3" t="s">
@@ -24654,7 +24636,7 @@
       </c>
     </row>
     <row r="706" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A706" s="8" t="s">
+      <c r="A706" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B706" s="2" t="s">
@@ -24680,7 +24662,7 @@
       </c>
     </row>
     <row r="707" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A707" s="8" t="s">
+      <c r="A707" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B707" s="3" t="s">
@@ -24706,7 +24688,7 @@
       </c>
     </row>
     <row r="708" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A708" s="8" t="s">
+      <c r="A708" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B708" s="2" t="s">
@@ -24732,7 +24714,7 @@
       </c>
     </row>
     <row r="709" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A709" s="8" t="s">
+      <c r="A709" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B709" s="3" t="s">
@@ -24758,7 +24740,7 @@
       </c>
     </row>
     <row r="710" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A710" s="8" t="s">
+      <c r="A710" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B710" s="2" t="s">
@@ -24784,7 +24766,7 @@
       </c>
     </row>
     <row r="711" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A711" s="8" t="s">
+      <c r="A711" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B711" s="3" t="s">
@@ -24810,7 +24792,7 @@
       </c>
     </row>
     <row r="712" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A712" s="8" t="s">
+      <c r="A712" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B712" s="2" t="s">
@@ -24836,7 +24818,7 @@
       </c>
     </row>
     <row r="713" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A713" s="8" t="s">
+      <c r="A713" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B713" s="3" t="s">
@@ -24862,7 +24844,7 @@
       </c>
     </row>
     <row r="714" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A714" s="8" t="s">
+      <c r="A714" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B714" s="2" t="s">
@@ -24888,7 +24870,7 @@
       </c>
     </row>
     <row r="715" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A715" s="8" t="s">
+      <c r="A715" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B715" s="3" t="s">
@@ -24914,7 +24896,7 @@
       </c>
     </row>
     <row r="716" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A716" s="8" t="s">
+      <c r="A716" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B716" s="2" t="s">
@@ -24940,7 +24922,7 @@
       </c>
     </row>
     <row r="717" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A717" s="8" t="s">
+      <c r="A717" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B717" s="3" t="s">
@@ -24966,7 +24948,7 @@
       </c>
     </row>
     <row r="718" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A718" s="8" t="s">
+      <c r="A718" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B718" s="2" t="s">
@@ -24992,7 +24974,7 @@
       </c>
     </row>
     <row r="719" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A719" s="8" t="s">
+      <c r="A719" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B719" s="3" t="s">
@@ -25018,7 +25000,7 @@
       </c>
     </row>
     <row r="720" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A720" s="8" t="s">
+      <c r="A720" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B720" s="2" t="s">
@@ -25044,7 +25026,7 @@
       </c>
     </row>
     <row r="721" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A721" s="8" t="s">
+      <c r="A721" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B721" s="3" t="s">
@@ -25070,7 +25052,7 @@
       </c>
     </row>
     <row r="722" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A722" s="8" t="s">
+      <c r="A722" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B722" s="2" t="s">
@@ -25096,7 +25078,7 @@
       </c>
     </row>
     <row r="723" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A723" s="8" t="s">
+      <c r="A723" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B723" s="3" t="s">
@@ -25122,7 +25104,7 @@
       </c>
     </row>
     <row r="724" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A724" s="8" t="s">
+      <c r="A724" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B724" s="2" t="s">
@@ -25148,7 +25130,7 @@
       </c>
     </row>
     <row r="725" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A725" s="8" t="s">
+      <c r="A725" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B725" s="3" t="s">
@@ -25174,7 +25156,7 @@
       </c>
     </row>
     <row r="726" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A726" s="8" t="s">
+      <c r="A726" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B726" s="2" t="s">
@@ -25200,7 +25182,7 @@
       </c>
     </row>
     <row r="727" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A727" s="8" t="s">
+      <c r="A727" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B727" s="3" t="s">
@@ -25226,7 +25208,7 @@
       </c>
     </row>
     <row r="728" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A728" s="8" t="s">
+      <c r="A728" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B728" s="2" t="s">
@@ -25252,7 +25234,7 @@
       </c>
     </row>
     <row r="729" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A729" s="8" t="s">
+      <c r="A729" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B729" s="3" t="s">
@@ -25278,7 +25260,7 @@
       </c>
     </row>
     <row r="730" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A730" s="8" t="s">
+      <c r="A730" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B730" s="2" t="s">
@@ -25304,7 +25286,7 @@
       </c>
     </row>
     <row r="731" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A731" s="8" t="s">
+      <c r="A731" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B731" s="3" t="s">
@@ -25330,7 +25312,7 @@
       </c>
     </row>
     <row r="732" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A732" s="8" t="s">
+      <c r="A732" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B732" s="2" t="s">
@@ -25356,7 +25338,7 @@
       </c>
     </row>
     <row r="733" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A733" s="8" t="s">
+      <c r="A733" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B733" s="3" t="s">
@@ -25382,7 +25364,7 @@
       </c>
     </row>
     <row r="734" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A734" s="8" t="s">
+      <c r="A734" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B734" s="2" t="s">
@@ -25408,7 +25390,7 @@
       </c>
     </row>
     <row r="735" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A735" s="8" t="s">
+      <c r="A735" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B735" s="3" t="s">
@@ -25434,7 +25416,7 @@
       </c>
     </row>
     <row r="736" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A736" s="8" t="s">
+      <c r="A736" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B736" s="2" t="s">
@@ -25460,7 +25442,7 @@
       </c>
     </row>
     <row r="737" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A737" s="8" t="s">
+      <c r="A737" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B737" s="3" t="s">
@@ -25485,8 +25467,8 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="738" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A738" s="8" t="s">
+    <row r="738" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A738" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B738" s="2" t="s">
@@ -25512,7 +25494,7 @@
       </c>
     </row>
     <row r="739" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A739" s="8" t="s">
+      <c r="A739" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B739" s="3" t="s">
@@ -25537,8 +25519,8 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="740" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A740" s="8" t="s">
+    <row r="740" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A740" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B740" s="2" t="s">
@@ -25564,7 +25546,7 @@
       </c>
     </row>
     <row r="741" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A741" s="8" t="s">
+      <c r="A741" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B741" s="3" t="s">
@@ -25590,7 +25572,7 @@
       </c>
     </row>
     <row r="742" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A742" s="8" t="s">
+      <c r="A742" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B742" s="2" t="s">
@@ -25616,7 +25598,7 @@
       </c>
     </row>
     <row r="743" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A743" s="8" t="s">
+      <c r="A743" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B743" s="3" t="s">
@@ -25642,7 +25624,7 @@
       </c>
     </row>
     <row r="744" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A744" s="8" t="s">
+      <c r="A744" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B744" s="2" t="s">
@@ -25668,7 +25650,7 @@
       </c>
     </row>
     <row r="745" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A745" s="8" t="s">
+      <c r="A745" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B745" s="3" t="s">
@@ -25694,7 +25676,7 @@
       </c>
     </row>
     <row r="746" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A746" s="8" t="s">
+      <c r="A746" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B746" s="2" t="s">
@@ -25720,7 +25702,7 @@
       </c>
     </row>
     <row r="747" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A747" s="8" t="s">
+      <c r="A747" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B747" s="3" t="s">
@@ -25746,7 +25728,7 @@
       </c>
     </row>
     <row r="748" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A748" s="8" t="s">
+      <c r="A748" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B748" s="2" t="s">
@@ -25772,7 +25754,7 @@
       </c>
     </row>
     <row r="749" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A749" s="8" t="s">
+      <c r="A749" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B749" s="3" t="s">
@@ -25798,7 +25780,7 @@
       </c>
     </row>
     <row r="750" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A750" s="8" t="s">
+      <c r="A750" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B750" s="2" t="s">
@@ -25824,7 +25806,7 @@
       </c>
     </row>
     <row r="751" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A751" s="8" t="s">
+      <c r="A751" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B751" s="3" t="s">
@@ -25850,7 +25832,7 @@
       </c>
     </row>
     <row r="752" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A752" s="8" t="s">
+      <c r="A752" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B752" s="2" t="s">
@@ -25876,7 +25858,7 @@
       </c>
     </row>
     <row r="753" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A753" s="8" t="s">
+      <c r="A753" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B753" s="3" t="s">
@@ -25902,7 +25884,7 @@
       </c>
     </row>
     <row r="754" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A754" s="8" t="s">
+      <c r="A754" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B754" s="2" t="s">
@@ -25928,7 +25910,7 @@
       </c>
     </row>
     <row r="755" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A755" s="8" t="s">
+      <c r="A755" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B755" s="3" t="s">
@@ -25954,7 +25936,7 @@
       </c>
     </row>
     <row r="756" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A756" s="8" t="s">
+      <c r="A756" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B756" s="2" t="s">
@@ -25980,7 +25962,7 @@
       </c>
     </row>
     <row r="757" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A757" s="8" t="s">
+      <c r="A757" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B757" s="3" t="s">
@@ -26006,7 +25988,7 @@
       </c>
     </row>
     <row r="758" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A758" s="8" t="s">
+      <c r="A758" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B758" s="2" t="s">
@@ -26032,7 +26014,7 @@
       </c>
     </row>
     <row r="759" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A759" s="8" t="s">
+      <c r="A759" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B759" s="3" t="s">
@@ -26057,8 +26039,8 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="760" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A760" s="8" t="s">
+    <row r="760" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A760" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B760" s="2" t="s">
@@ -26084,7 +26066,7 @@
       </c>
     </row>
     <row r="761" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A761" s="8" t="s">
+      <c r="A761" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B761" s="3" t="s">
@@ -26109,8 +26091,8 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="762" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A762" s="8" t="s">
+    <row r="762" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A762" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B762" s="2" t="s">
@@ -26136,7 +26118,7 @@
       </c>
     </row>
     <row r="763" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A763" s="8" t="s">
+      <c r="A763" s="6" t="s">
         <v>1678</v>
       </c>
       <c r="B763" s="3" t="s">
@@ -26162,7 +26144,7 @@
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A764" s="8" t="s">
+      <c r="A764" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B764" s="2" t="s">
@@ -26188,7 +26170,7 @@
       </c>
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A765" s="8" t="s">
+      <c r="A765" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B765" s="3" t="s">
@@ -26214,7 +26196,7 @@
       </c>
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A766" s="8" t="s">
+      <c r="A766" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B766" s="2" t="s">
@@ -26240,7 +26222,7 @@
       </c>
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A767" s="8" t="s">
+      <c r="A767" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B767" s="3" t="s">
@@ -26266,7 +26248,7 @@
       </c>
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A768" s="8" t="s">
+      <c r="A768" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B768" s="2" t="s">
@@ -26292,7 +26274,7 @@
       </c>
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A769" s="8" t="s">
+      <c r="A769" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B769" s="3" t="s">
@@ -26318,7 +26300,7 @@
       </c>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A770" s="8" t="s">
+      <c r="A770" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B770" s="2" t="s">
@@ -26344,7 +26326,7 @@
       </c>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A771" s="8" t="s">
+      <c r="A771" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B771" s="3" t="s">
@@ -26370,7 +26352,7 @@
       </c>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A772" s="8" t="s">
+      <c r="A772" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B772" s="2" t="s">
@@ -26396,7 +26378,7 @@
       </c>
     </row>
     <row r="773" spans="1:8" ht="45" x14ac:dyDescent="0.15">
-      <c r="A773" s="8" t="s">
+      <c r="A773" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B773" s="3" t="s">
@@ -26422,7 +26404,7 @@
       </c>
     </row>
     <row r="774" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A774" s="8" t="s">
+      <c r="A774" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B774" s="2" t="s">
@@ -26448,7 +26430,7 @@
       </c>
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A775" s="8" t="s">
+      <c r="A775" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B775" s="3" t="s">
@@ -26474,7 +26456,7 @@
       </c>
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A776" s="8" t="s">
+      <c r="A776" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B776" s="2" t="s">
@@ -26500,7 +26482,7 @@
       </c>
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A777" s="8" t="s">
+      <c r="A777" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B777" s="3" t="s">
@@ -26526,7 +26508,7 @@
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A778" s="8" t="s">
+      <c r="A778" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B778" s="2" t="s">
@@ -26552,7 +26534,7 @@
       </c>
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A779" s="8" t="s">
+      <c r="A779" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B779" s="3" t="s">
@@ -26578,7 +26560,7 @@
       </c>
     </row>
     <row r="780" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A780" s="8" t="s">
+      <c r="A780" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B780" s="2" t="s">
@@ -26604,7 +26586,7 @@
       </c>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A781" s="8" t="s">
+      <c r="A781" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B781" s="3" t="s">
@@ -26630,7 +26612,7 @@
       </c>
     </row>
     <row r="782" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A782" s="8" t="s">
+      <c r="A782" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B782" s="2" t="s">
@@ -26656,7 +26638,7 @@
       </c>
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A783" s="8" t="s">
+      <c r="A783" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B783" s="3" t="s">
@@ -26682,7 +26664,7 @@
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A784" s="8" t="s">
+      <c r="A784" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B784" s="2" t="s">
@@ -26708,7 +26690,7 @@
       </c>
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A785" s="8" t="s">
+      <c r="A785" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B785" s="3" t="s">
@@ -26734,7 +26716,7 @@
       </c>
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A786" s="8" t="s">
+      <c r="A786" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B786" s="2" t="s">
@@ -26760,7 +26742,7 @@
       </c>
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A787" s="8" t="s">
+      <c r="A787" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B787" s="3" t="s">
@@ -26786,7 +26768,7 @@
       </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A788" s="8" t="s">
+      <c r="A788" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B788" s="2" t="s">
@@ -26812,7 +26794,7 @@
       </c>
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A789" s="8" t="s">
+      <c r="A789" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B789" s="3" t="s">
@@ -26838,7 +26820,7 @@
       </c>
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A790" s="8" t="s">
+      <c r="A790" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B790" s="2" t="s">
@@ -26864,7 +26846,7 @@
       </c>
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A791" s="8" t="s">
+      <c r="A791" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B791" s="3" t="s">
@@ -26890,7 +26872,7 @@
       </c>
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A792" s="8" t="s">
+      <c r="A792" s="6" t="s">
         <v>1829</v>
       </c>
       <c r="B792" s="2" t="s">
@@ -26916,7 +26898,7 @@
       </c>
     </row>
     <row r="793" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A793" s="8" t="s">
+      <c r="A793" s="6" t="s">
         <v>1953</v>
       </c>
       <c r="B793" s="3" t="s">
@@ -26930,7 +26912,7 @@
       </c>
     </row>
     <row r="794" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A794" s="8" t="s">
+      <c r="A794" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B794" s="2" t="s">
@@ -26944,7 +26926,7 @@
       </c>
     </row>
     <row r="795" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A795" s="8" t="s">
+      <c r="A795" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B795" s="3" t="s">
@@ -26958,7 +26940,7 @@
       </c>
     </row>
     <row r="796" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A796" s="8" t="s">
+      <c r="A796" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B796" s="2" t="s">
@@ -26972,7 +26954,7 @@
       </c>
     </row>
     <row r="797" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A797" s="8" t="s">
+      <c r="A797" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B797" s="3" t="s">
@@ -26986,7 +26968,7 @@
       </c>
     </row>
     <row r="798" spans="1:8" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A798" s="8" t="s">
+      <c r="A798" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B798" s="2" t="s">
@@ -27000,7 +26982,7 @@
       </c>
     </row>
     <row r="799" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A799" s="8" t="s">
+      <c r="A799" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B799" s="3" t="s">
@@ -27013,8 +26995,8 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="800" spans="1:8" ht="45" x14ac:dyDescent="0.15">
-      <c r="A800" s="8" t="s">
+    <row r="800" spans="1:8" ht="33.75" x14ac:dyDescent="0.15">
+      <c r="A800" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B800" s="2" t="s">
@@ -27028,7 +27010,7 @@
       </c>
     </row>
     <row r="801" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A801" s="8" t="s">
+      <c r="A801" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B801" s="3" t="s">
@@ -27042,7 +27024,7 @@
       </c>
     </row>
     <row r="802" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A802" s="8" t="s">
+      <c r="A802" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B802" s="2" t="s">
@@ -27056,7 +27038,7 @@
       </c>
     </row>
     <row r="803" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A803" s="8" t="s">
+      <c r="A803" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B803" s="3" t="s">
@@ -27069,8 +27051,8 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="804" spans="1:4" ht="45" x14ac:dyDescent="0.15">
-      <c r="A804" s="8" t="s">
+    <row r="804" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
+      <c r="A804" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B804" s="2" t="s">
@@ -27084,7 +27066,7 @@
       </c>
     </row>
     <row r="805" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A805" s="8" t="s">
+      <c r="A805" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B805" s="3" t="s">
@@ -27098,7 +27080,7 @@
       </c>
     </row>
     <row r="806" spans="1:4" ht="45" x14ac:dyDescent="0.15">
-      <c r="A806" s="8" t="s">
+      <c r="A806" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B806" s="2" t="s">
@@ -27111,8 +27093,8 @@
         <v>197</v>
       </c>
     </row>
-    <row r="807" spans="1:4" ht="56.25" x14ac:dyDescent="0.15">
-      <c r="A807" s="8" t="s">
+    <row r="807" spans="1:4" ht="45" x14ac:dyDescent="0.15">
+      <c r="A807" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B807" s="3" t="s">
@@ -27126,7 +27108,7 @@
       </c>
     </row>
     <row r="808" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A808" s="8" t="s">
+      <c r="A808" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B808" s="2" t="s">
@@ -27140,7 +27122,7 @@
       </c>
     </row>
     <row r="809" spans="1:4" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A809" s="8" t="s">
+      <c r="A809" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B809" s="3" t="s">
@@ -27154,7 +27136,7 @@
       </c>
     </row>
     <row r="810" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A810" s="8" t="s">
+      <c r="A810" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B810" s="2" t="s">
@@ -27168,7 +27150,7 @@
       </c>
     </row>
     <row r="811" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A811" s="8" t="s">
+      <c r="A811" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B811" s="3" t="s">
@@ -27181,8 +27163,8 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="812" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A812" s="8" t="s">
+    <row r="812" spans="1:4" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A812" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B812" s="2" t="s">
@@ -27196,7 +27178,7 @@
       </c>
     </row>
     <row r="813" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A813" s="8" t="s">
+      <c r="A813" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B813" s="3" t="s">
@@ -27210,7 +27192,7 @@
       </c>
     </row>
     <row r="814" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="A814" s="8" t="s">
+      <c r="A814" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B814" s="2" t="s">
@@ -27223,8 +27205,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="815" spans="1:4" ht="45" x14ac:dyDescent="0.15">
-      <c r="A815" s="8" t="s">
+    <row r="815" spans="1:4" ht="33.75" x14ac:dyDescent="0.15">
+      <c r="A815" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B815" s="3" t="s">
@@ -27238,7 +27220,7 @@
       </c>
     </row>
     <row r="816" spans="1:4" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A816" s="8" t="s">
+      <c r="A816" s="6" t="s">
         <v>1915</v>
       </c>
       <c r="B816" s="2" t="s">
